--- a/research/traditional_assets/database/data/sweden/sweden_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_semiconductor_equip.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.094</v>
+        <v>0.188</v>
       </c>
       <c r="G2">
-        <v>-0.3097813308252998</v>
+        <v>-0.8725575508266752</v>
       </c>
       <c r="H2">
-        <v>-0.4837761580061133</v>
+        <v>-1.094850090973815</v>
       </c>
       <c r="I2">
-        <v>-0.9169997648718551</v>
+        <v>-0.9896368958152044</v>
       </c>
       <c r="J2">
-        <v>-0.9169997648718551</v>
+        <v>-0.9896368958152044</v>
       </c>
       <c r="K2">
-        <v>-18.84</v>
+        <v>-12.842</v>
       </c>
       <c r="L2">
-        <v>-1.107453562191394</v>
+        <v>-1.015900640772091</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15.028</v>
+        <v>4.935</v>
       </c>
       <c r="V2">
-        <v>0.09571974522292993</v>
+        <v>0.04973795605724652</v>
       </c>
       <c r="W2">
-        <v>-1.223300970873786</v>
+        <v>-0.4272727272727273</v>
       </c>
       <c r="X2">
-        <v>0.09651557129745518</v>
+        <v>0.1637376012900802</v>
       </c>
       <c r="Y2">
-        <v>-1.319816542171242</v>
+        <v>-0.5910103285628074</v>
       </c>
       <c r="Z2">
-        <v>0.4452587222236763</v>
+        <v>0.2759380934710003</v>
       </c>
       <c r="AA2">
-        <v>-0.4295500833179041</v>
+        <v>-0.2759752368165884</v>
       </c>
       <c r="AB2">
-        <v>0.09190381237533395</v>
+        <v>0.1547361608064224</v>
       </c>
       <c r="AC2">
-        <v>-0.5219766641401279</v>
+        <v>-0.432039470587377</v>
       </c>
       <c r="AD2">
-        <v>26.247</v>
+        <v>21.806</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26.247</v>
+        <v>21.806</v>
       </c>
       <c r="AG2">
-        <v>11.219</v>
+        <v>16.871</v>
       </c>
       <c r="AH2">
-        <v>0.1432329042221701</v>
+        <v>0.1801761604944392</v>
       </c>
       <c r="AI2">
-        <v>0.4314173474251713</v>
+        <v>0.41798769384117</v>
       </c>
       <c r="AJ2">
-        <v>0.06669282304614818</v>
+        <v>0.1453256497058342</v>
       </c>
       <c r="AK2">
-        <v>0.2448975136975836</v>
+        <v>0.3571791506118474</v>
       </c>
       <c r="AL2">
-        <v>2.208</v>
+        <v>2.123</v>
       </c>
       <c r="AM2">
-        <v>1.991</v>
+        <v>1.757</v>
       </c>
       <c r="AN2">
-        <v>-2.101441152922338</v>
+        <v>-2.872612304044263</v>
       </c>
       <c r="AO2">
-        <v>-7.065217391304347</v>
+        <v>-5.892604804521904</v>
       </c>
       <c r="AP2">
-        <v>-0.8982385908726982</v>
+        <v>-2.222500329337374</v>
       </c>
       <c r="AQ2">
-        <v>-7.835258663987945</v>
+        <v>-7.120091064314173</v>
       </c>
     </row>
     <row r="3">
@@ -716,22 +716,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.4560975609756098</v>
+        <v>-1.398876404494382</v>
       </c>
       <c r="H3">
-        <v>-0.5471544715447154</v>
+        <v>-1.615168539325843</v>
       </c>
       <c r="I3">
-        <v>-0.8943089430894309</v>
+        <v>-1.095505617977528</v>
       </c>
       <c r="J3">
-        <v>-0.8943089430894309</v>
+        <v>-1.095505617977528</v>
       </c>
       <c r="K3">
-        <v>-14</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L3">
-        <v>-1.138211382113821</v>
+        <v>-1.188202247191011</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,73 +755,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.2</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
-        <v>0.1418581418581419</v>
+        <v>0.03226666666666667</v>
       </c>
       <c r="W3">
-        <v>-1.635514018691589</v>
+        <v>-0.4272727272727273</v>
       </c>
       <c r="X3">
-        <v>0.1074227349319237</v>
+        <v>0.1816593467875551</v>
       </c>
       <c r="Y3">
-        <v>-1.742936753623512</v>
+        <v>-0.6089320740602824</v>
       </c>
       <c r="Z3">
-        <v>0.4104104104104104</v>
+        <v>0.2373333333333333</v>
       </c>
       <c r="AA3">
-        <v>-0.3670337003670336</v>
+        <v>-0.26</v>
       </c>
       <c r="AB3">
-        <v>0.09072110741693755</v>
+        <v>0.1520385969535773</v>
       </c>
       <c r="AC3">
-        <v>-0.4577548077839712</v>
+        <v>-0.4120385969535773</v>
       </c>
       <c r="AD3">
-        <v>24.4</v>
+        <v>20.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>24.4</v>
+        <v>20.5</v>
       </c>
       <c r="AG3">
-        <v>10.2</v>
+        <v>18.08</v>
       </c>
       <c r="AH3">
-        <v>0.1959839357429719</v>
+        <v>0.2146596858638743</v>
       </c>
       <c r="AI3">
-        <v>0.5520361990950226</v>
+        <v>0.4987834549878346</v>
       </c>
       <c r="AJ3">
-        <v>0.09247506799637352</v>
+        <v>0.1942415126772669</v>
       </c>
       <c r="AK3">
-        <v>0.34</v>
+        <v>0.467425025853154</v>
       </c>
       <c r="AL3">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AM3">
-        <v>2.057</v>
+        <v>1.881</v>
       </c>
       <c r="AN3">
-        <v>-2.368932038834951</v>
+        <v>-3.059701492537313</v>
       </c>
       <c r="AO3">
-        <v>-5.188679245283018</v>
+        <v>-3.979591836734694</v>
       </c>
       <c r="AP3">
-        <v>-0.9902912621359222</v>
+        <v>-2.698507462686567</v>
       </c>
       <c r="AQ3">
-        <v>-5.347593582887701</v>
+        <v>-4.146730462519936</v>
       </c>
     </row>
     <row r="4">
@@ -847,16 +847,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.558282208588956</v>
+        <v>-6.839186691312384</v>
       </c>
       <c r="J4">
-        <v>-3.558282208588956</v>
+        <v>-6.839186691312384</v>
       </c>
       <c r="K4">
-        <v>-2.32</v>
+        <v>-3.68</v>
       </c>
       <c r="L4">
-        <v>-3.558282208588956</v>
+        <v>-6.802218114602588</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,67 +880,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.78</v>
+        <v>2.37</v>
       </c>
       <c r="V4">
-        <v>0.02574257425742574</v>
+        <v>0.265695067264574</v>
       </c>
       <c r="W4">
-        <v>-0.3040629095674967</v>
+        <v>-0.2609929078014185</v>
       </c>
       <c r="X4">
-        <v>0.09262821183786592</v>
+        <v>0.156873525724698</v>
       </c>
       <c r="Y4">
-        <v>-0.3966911214053626</v>
+        <v>-0.4178664335261165</v>
       </c>
       <c r="Z4">
-        <v>0.1207183854841696</v>
+        <v>0.04035205489669576</v>
       </c>
       <c r="AA4">
-        <v>-0.4295500833179041</v>
+        <v>-0.2759752368165884</v>
       </c>
       <c r="AB4">
-        <v>0.09242658082222384</v>
+        <v>0.1560642337707886</v>
       </c>
       <c r="AC4">
-        <v>-0.5219766641401279</v>
+        <v>-0.432039470587377</v>
       </c>
       <c r="AD4">
-        <v>0.08699999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.08699999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="AG4">
-        <v>-0.6930000000000001</v>
+        <v>-2.304</v>
       </c>
       <c r="AH4">
-        <v>0.002863066442886761</v>
+        <v>0.007344758513242822</v>
       </c>
       <c r="AI4">
-        <v>0.006132374709240854</v>
+        <v>0.00697969543147208</v>
       </c>
       <c r="AJ4">
-        <v>-0.02340662681122708</v>
+        <v>-0.3482466747279324</v>
       </c>
       <c r="AK4">
-        <v>-0.05168941597672858</v>
+        <v>-0.3251481795088908</v>
       </c>
       <c r="AL4">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="AM4">
-        <v>-0.004</v>
+        <v>0.011</v>
       </c>
       <c r="AO4">
-        <v>-1160</v>
+        <v>-336.3636363636364</v>
       </c>
       <c r="AQ4">
-        <v>580</v>
+        <v>-336.3636363636364</v>
       </c>
     </row>
     <row r="5">
@@ -960,25 +960,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.094</v>
+        <v>0.188</v>
       </c>
       <c r="G5">
-        <v>0.08374384236453204</v>
+        <v>-0.214859437751004</v>
       </c>
       <c r="H5">
-        <v>-0.3694581280788178</v>
+        <v>-0.4698795180722891</v>
       </c>
       <c r="I5">
-        <v>-0.5615763546798029</v>
+        <v>-0.2028112449799197</v>
       </c>
       <c r="J5">
-        <v>-0.5615763546798029</v>
+        <v>-0.2028112449799197</v>
       </c>
       <c r="K5">
-        <v>-2.52</v>
+        <v>-0.702</v>
       </c>
       <c r="L5">
-        <v>-0.6206896551724138</v>
+        <v>-0.1409638554216867</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,73 +1002,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.048</v>
+        <v>0.145</v>
       </c>
       <c r="V5">
-        <v>0.001804511278195489</v>
+        <v>0.009477124183006535</v>
       </c>
       <c r="W5">
-        <v>-1.223300970873786</v>
+        <v>-1.014450867052023</v>
       </c>
       <c r="X5">
-        <v>0.09651557129745518</v>
+        <v>0.1637376012900802</v>
       </c>
       <c r="Y5">
-        <v>-1.319816542171242</v>
+        <v>-1.178188468342103</v>
       </c>
       <c r="Z5">
-        <v>1.431593794076164</v>
+        <v>2.071547420965059</v>
       </c>
       <c r="AA5">
-        <v>-0.8039492242595204</v>
+        <v>-0.4201331114808652</v>
       </c>
       <c r="AB5">
-        <v>0.09190381237533395</v>
+        <v>0.1547361608064224</v>
       </c>
       <c r="AC5">
-        <v>-0.8958530366348544</v>
+        <v>-0.5748692722872877</v>
       </c>
       <c r="AD5">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="AG5">
-        <v>1.712</v>
+        <v>1.095</v>
       </c>
       <c r="AH5">
-        <v>0.0620592383638928</v>
+        <v>0.07496977025392987</v>
       </c>
       <c r="AI5">
-        <v>0.7177814029363785</v>
+        <v>0.768753874767514</v>
       </c>
       <c r="AJ5">
-        <v>0.06046905905623057</v>
+        <v>0.06678865507776761</v>
       </c>
       <c r="AK5">
-        <v>0.7121464226289518</v>
+        <v>0.7459128065395095</v>
       </c>
       <c r="AL5">
-        <v>0.08599999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="AM5">
-        <v>-0.062</v>
+        <v>-0.135</v>
       </c>
       <c r="AN5">
-        <v>-0.8036529680365297</v>
+        <v>-1.391694725028058</v>
       </c>
       <c r="AO5">
-        <v>-26.51162790697675</v>
+        <v>-6.644736842105264</v>
       </c>
       <c r="AP5">
-        <v>-0.7817351598173516</v>
+        <v>-1.228956228956229</v>
       </c>
       <c r="AQ5">
-        <v>36.7741935483871</v>
+        <v>7.481481481481483</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_semiconductor_equip.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.188</v>
+        <v>0.224</v>
       </c>
       <c r="G2">
-        <v>-0.8725575508266752</v>
+        <v>-0.6912150790979469</v>
       </c>
       <c r="H2">
-        <v>-1.094850090973815</v>
+        <v>-1.003904409289801</v>
       </c>
       <c r="I2">
-        <v>-0.9896368958152044</v>
+        <v>-1.642073375967688</v>
       </c>
       <c r="J2">
-        <v>-0.9896368958152044</v>
+        <v>-1.642073375967688</v>
       </c>
       <c r="K2">
-        <v>-12.842</v>
+        <v>-22.731</v>
       </c>
       <c r="L2">
-        <v>-1.015900640772091</v>
+        <v>-1.530191854594413</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.935</v>
+        <v>8.228999999999999</v>
       </c>
       <c r="V2">
-        <v>0.04973795605724652</v>
+        <v>0.1469726736917306</v>
       </c>
       <c r="W2">
-        <v>-0.4272727272727273</v>
+        <v>-0.7265415549597856</v>
       </c>
       <c r="X2">
-        <v>0.1637376012900802</v>
+        <v>0.1376974363752175</v>
       </c>
       <c r="Y2">
-        <v>-0.5910103285628074</v>
+        <v>-0.864238991335003</v>
       </c>
       <c r="Z2">
-        <v>0.2759380934710003</v>
+        <v>0.3144980310793073</v>
       </c>
       <c r="AA2">
-        <v>-0.2759752368165884</v>
+        <v>-0.4963805584281282</v>
       </c>
       <c r="AB2">
-        <v>0.1547361608064224</v>
+        <v>0.1277983857609803</v>
       </c>
       <c r="AC2">
-        <v>-0.432039470587377</v>
+        <v>-0.6185539098261625</v>
       </c>
       <c r="AD2">
-        <v>21.806</v>
+        <v>24.584</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21.806</v>
+        <v>24.584</v>
       </c>
       <c r="AG2">
-        <v>16.871</v>
+        <v>16.355</v>
       </c>
       <c r="AH2">
-        <v>0.1801761604944392</v>
+        <v>0.3051108297962122</v>
       </c>
       <c r="AI2">
-        <v>0.41798769384117</v>
+        <v>0.4592221765606904</v>
       </c>
       <c r="AJ2">
-        <v>0.1453256497058342</v>
+        <v>0.2260695279563204</v>
       </c>
       <c r="AK2">
-        <v>0.3571791506118474</v>
+        <v>0.3609976823750138</v>
       </c>
       <c r="AL2">
-        <v>2.123</v>
+        <v>2.697</v>
       </c>
       <c r="AM2">
-        <v>1.757</v>
+        <v>-0.7669999999999999</v>
       </c>
       <c r="AN2">
-        <v>-2.872612304044263</v>
+        <v>-1.024717602434246</v>
       </c>
       <c r="AO2">
-        <v>-5.892604804521904</v>
+        <v>-9.044493882091212</v>
       </c>
       <c r="AP2">
-        <v>-2.222500329337374</v>
+        <v>-0.6817139760743612</v>
       </c>
       <c r="AQ2">
-        <v>-7.120091064314173</v>
+        <v>31.80312907431552</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Midsummer AB (publ) (OM:MIDS)</t>
+          <t>Obducat AB (publ) (NGM:OBDU B)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,23 +715,26 @@
           <t>Semiconductor Equip</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.146</v>
+      </c>
       <c r="G3">
-        <v>-1.398876404494382</v>
+        <v>0.133287858117326</v>
       </c>
       <c r="H3">
-        <v>-1.615168539325843</v>
+        <v>-0.1259208731241473</v>
       </c>
       <c r="I3">
-        <v>-1.095505617977528</v>
+        <v>-0.06316507503410641</v>
       </c>
       <c r="J3">
-        <v>-1.095505617977528</v>
+        <v>-0.06316507503410641</v>
       </c>
       <c r="K3">
-        <v>-8.460000000000001</v>
+        <v>-0.271</v>
       </c>
       <c r="L3">
-        <v>-1.188202247191011</v>
+        <v>-0.03697135061391542</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.42</v>
+        <v>0.629</v>
       </c>
       <c r="V3">
-        <v>0.03226666666666667</v>
+        <v>0.02588477366255144</v>
       </c>
       <c r="W3">
-        <v>-0.4272727272727273</v>
+        <v>-0.7265415549597856</v>
       </c>
       <c r="X3">
-        <v>0.1816593467875551</v>
+        <v>0.1376974363752175</v>
       </c>
       <c r="Y3">
-        <v>-0.6089320740602824</v>
+        <v>-0.864238991335003</v>
       </c>
       <c r="Z3">
-        <v>0.2373333333333333</v>
+        <v>4.993188010899183</v>
       </c>
       <c r="AA3">
-        <v>-0.26</v>
+        <v>-0.3153950953678474</v>
       </c>
       <c r="AB3">
-        <v>0.1520385969535773</v>
+        <v>0.1277983857609803</v>
       </c>
       <c r="AC3">
-        <v>-0.4120385969535773</v>
+        <v>-0.4431934811288277</v>
       </c>
       <c r="AD3">
-        <v>20.5</v>
+        <v>2.82</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>20.5</v>
+        <v>2.82</v>
       </c>
       <c r="AG3">
-        <v>18.08</v>
+        <v>2.191</v>
       </c>
       <c r="AH3">
-        <v>0.2146596858638743</v>
+        <v>0.1039823008849557</v>
       </c>
       <c r="AI3">
-        <v>0.4987834549878346</v>
+        <v>0.8468468468468467</v>
       </c>
       <c r="AJ3">
-        <v>0.1942415126772669</v>
+        <v>0.08270733456645653</v>
       </c>
       <c r="AK3">
-        <v>0.467425025853154</v>
+        <v>0.8111810440577565</v>
       </c>
       <c r="AL3">
-        <v>1.96</v>
+        <v>0.427</v>
       </c>
       <c r="AM3">
-        <v>1.881</v>
+        <v>0.427</v>
       </c>
       <c r="AN3">
-        <v>-3.059701492537313</v>
+        <v>-7.212276214833759</v>
       </c>
       <c r="AO3">
-        <v>-3.979591836734694</v>
+        <v>-1.084309133489461</v>
       </c>
       <c r="AP3">
-        <v>-2.698507462686567</v>
+        <v>-5.603580562659846</v>
       </c>
       <c r="AQ3">
-        <v>-4.146730462519936</v>
+        <v>-1.084309133489461</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Smoltek Nanotech Holding AB (NGM:SMOL)</t>
+          <t>Midsummer AB (publ) (OM:MIDS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,22 +844,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-1.216133942161339</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>-1.482496194824962</v>
       </c>
       <c r="I4">
-        <v>-6.839186691312384</v>
+        <v>-2.922374429223744</v>
       </c>
       <c r="J4">
-        <v>-6.839186691312384</v>
+        <v>-2.922374429223744</v>
       </c>
       <c r="K4">
-        <v>-3.68</v>
+        <v>-17.6</v>
       </c>
       <c r="L4">
-        <v>-6.802218114602588</v>
+        <v>-2.678843226788433</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,67 +883,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.37</v>
+        <v>6.37</v>
       </c>
       <c r="V4">
-        <v>0.265695067264574</v>
+        <v>0.271063829787234</v>
       </c>
       <c r="W4">
-        <v>-0.2609929078014185</v>
+        <v>-0.854368932038835</v>
       </c>
       <c r="X4">
-        <v>0.156873525724698</v>
+        <v>0.1957458582123894</v>
       </c>
       <c r="Y4">
-        <v>-0.4178664335261165</v>
+        <v>-1.050114790251224</v>
       </c>
       <c r="Z4">
-        <v>0.04035205489669576</v>
+        <v>0.1698552223371251</v>
       </c>
       <c r="AA4">
-        <v>-0.2759752368165884</v>
+        <v>-0.4963805584281282</v>
       </c>
       <c r="AB4">
-        <v>0.1560642337707886</v>
+        <v>0.1221733513980344</v>
       </c>
       <c r="AC4">
-        <v>-0.432039470587377</v>
+        <v>-0.6185539098261625</v>
       </c>
       <c r="AD4">
-        <v>0.066</v>
+        <v>21.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.066</v>
+        <v>21.7</v>
       </c>
       <c r="AG4">
-        <v>-2.304</v>
+        <v>15.33</v>
       </c>
       <c r="AH4">
-        <v>0.007344758513242822</v>
+        <v>0.4800884955752212</v>
       </c>
       <c r="AI4">
-        <v>0.00697969543147208</v>
+        <v>0.5216346153846154</v>
       </c>
       <c r="AJ4">
-        <v>-0.3482466747279324</v>
+        <v>0.3947978367241823</v>
       </c>
       <c r="AK4">
-        <v>-0.3251481795088908</v>
+        <v>0.4351405052512063</v>
       </c>
       <c r="AL4">
-        <v>0.011</v>
+        <v>2.27</v>
       </c>
       <c r="AM4">
-        <v>0.011</v>
+        <v>-1.19</v>
+      </c>
+      <c r="AN4">
+        <v>-1.142105263157895</v>
       </c>
       <c r="AO4">
-        <v>-336.3636363636364</v>
+        <v>-8.458149779735683</v>
+      </c>
+      <c r="AP4">
+        <v>-0.8068421052631578</v>
       </c>
       <c r="AQ4">
-        <v>-336.3636363636364</v>
+        <v>16.1344537815126</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Obducat AB (publ) (NGM:OBDU B)</t>
+          <t>Smoltek Nanotech Holding AB (NGM:SMOL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,25 +969,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.188</v>
+        <v>0.302</v>
       </c>
       <c r="G5">
-        <v>-0.214859437751004</v>
+        <v>-3.408376963350785</v>
       </c>
       <c r="H5">
-        <v>-0.4698795180722891</v>
+        <v>-4.450261780104713</v>
       </c>
       <c r="I5">
-        <v>-0.2028112449799197</v>
+        <v>-4.952879581151833</v>
       </c>
       <c r="J5">
-        <v>-0.2028112449799197</v>
+        <v>-4.952879581151833</v>
       </c>
       <c r="K5">
-        <v>-0.702</v>
+        <v>-4.86</v>
       </c>
       <c r="L5">
-        <v>-0.1409638554216867</v>
+        <v>-5.089005235602095</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,73 +1011,70 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.145</v>
+        <v>1.23</v>
       </c>
       <c r="V5">
-        <v>0.009477124183006535</v>
+        <v>0.1501831501831502</v>
       </c>
       <c r="W5">
-        <v>-1.014450867052023</v>
+        <v>-0.5175718849840255</v>
       </c>
       <c r="X5">
-        <v>0.1637376012900802</v>
+        <v>0.1299153944332784</v>
       </c>
       <c r="Y5">
-        <v>-1.178188468342103</v>
+        <v>-0.6474872794173039</v>
       </c>
       <c r="Z5">
-        <v>2.071547420965059</v>
+        <v>0.1347727914197008</v>
       </c>
       <c r="AA5">
-        <v>-0.4201331114808652</v>
+        <v>-0.6675134067174711</v>
       </c>
       <c r="AB5">
-        <v>0.1547361608064224</v>
+        <v>0.1292375764468804</v>
       </c>
       <c r="AC5">
-        <v>-0.5748692722872877</v>
+        <v>-0.7967509831643514</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>0.064</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.24</v>
+        <v>0.064</v>
       </c>
       <c r="AG5">
-        <v>1.095</v>
+        <v>-1.166</v>
       </c>
       <c r="AH5">
-        <v>0.07496977025392987</v>
+        <v>0.007753816331475648</v>
       </c>
       <c r="AI5">
-        <v>0.768753874767514</v>
+        <v>0.007438400743840075</v>
       </c>
       <c r="AJ5">
-        <v>0.06678865507776761</v>
+        <v>-0.166002277904328</v>
       </c>
       <c r="AK5">
-        <v>0.7459128065395095</v>
+        <v>-0.1581231353403852</v>
       </c>
       <c r="AL5">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.135</v>
+        <v>-0.004</v>
       </c>
       <c r="AN5">
-        <v>-1.391694725028058</v>
-      </c>
-      <c r="AO5">
-        <v>-6.644736842105264</v>
+        <v>-0.01391304347826087</v>
       </c>
       <c r="AP5">
-        <v>-1.228956228956229</v>
+        <v>0.2534782608695652</v>
       </c>
       <c r="AQ5">
-        <v>7.481481481481483</v>
+        <v>1182.5</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_semiconductor_equip.xlsx
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1531,22 +1531,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1310384430970086</v>
+        <v>0.1308042339042288</v>
       </c>
       <c r="C2">
-        <v>19.42646088319764</v>
+        <v>19.27992774700412</v>
       </c>
       <c r="D2">
-        <v>19.29646088319764</v>
+        <v>19.34962774700412</v>
       </c>
       <c r="E2">
-        <v>-2.67</v>
+        <v>-2.4703</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1997</v>
       </c>
       <c r="G2">
         <v>0.13</v>
@@ -1567,28 +1567,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01004491</v>
       </c>
       <c r="N2">
-        <v>1.209666666666667</v>
+        <v>1.199621756666667</v>
       </c>
       <c r="O2">
-        <v>0.2491913333333333</v>
+        <v>0.2471220818733334</v>
       </c>
       <c r="P2">
-        <v>0.9604753333333333</v>
+        <v>0.9524996747933333</v>
       </c>
       <c r="Q2">
-        <v>1.117475333333333</v>
+        <v>1.109499674793333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1310384430970086</v>
+        <v>0.1317220726305341</v>
       </c>
       <c r="T2">
-        <v>1.968555267829298</v>
+        <v>1.984343478765222</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>120.4258342450721</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1308042339042288</v>
+        <v>0.1305700247114489</v>
       </c>
       <c r="C3">
-        <v>19.27992774700412</v>
+        <v>19.13368839787267</v>
       </c>
       <c r="D3">
-        <v>19.34962774700412</v>
+        <v>19.40308839787267</v>
       </c>
       <c r="E3">
-        <v>-2.4703</v>
+        <v>-2.2706</v>
       </c>
       <c r="F3">
-        <v>0.1997</v>
+        <v>0.3994</v>
       </c>
       <c r="G3">
         <v>0.13</v>
@@ -1649,28 +1649,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M3">
-        <v>0.01004491</v>
+        <v>0.02008982</v>
       </c>
       <c r="N3">
-        <v>1.199621756666667</v>
+        <v>1.189576846666667</v>
       </c>
       <c r="O3">
-        <v>0.2471220818733334</v>
+        <v>0.2450528304133334</v>
       </c>
       <c r="P3">
-        <v>0.9524996747933333</v>
+        <v>0.9445240162533334</v>
       </c>
       <c r="Q3">
-        <v>1.109499674793333</v>
+        <v>1.101524016253333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1317220726305341</v>
+        <v>0.1324196537871928</v>
       </c>
       <c r="T3">
-        <v>1.984343478765222</v>
+        <v>2.000453898087593</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>120.4258342450721</v>
+        <v>60.21291712253603</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1695,22 +1695,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1305700247114489</v>
+        <v>0.130335815518669</v>
       </c>
       <c r="C4">
-        <v>19.13368839787267</v>
+        <v>18.98774527764274</v>
       </c>
       <c r="D4">
-        <v>19.40308839787267</v>
+        <v>19.45684527764274</v>
       </c>
       <c r="E4">
-        <v>-2.2706</v>
+        <v>-2.0709</v>
       </c>
       <c r="F4">
-        <v>0.3994</v>
+        <v>0.5991</v>
       </c>
       <c r="G4">
         <v>0.13</v>
@@ -1731,28 +1731,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M4">
-        <v>0.02008982</v>
+        <v>0.03013473</v>
       </c>
       <c r="N4">
-        <v>1.189576846666667</v>
+        <v>1.179531936666667</v>
       </c>
       <c r="O4">
-        <v>0.2450528304133334</v>
+        <v>0.2429835789533334</v>
       </c>
       <c r="P4">
-        <v>0.9445240162533334</v>
+        <v>0.9365483577133334</v>
       </c>
       <c r="Q4">
-        <v>1.101524016253333</v>
+        <v>1.093548357713333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1324196537871928</v>
+        <v>0.1331316180604835</v>
       </c>
       <c r="T4">
-        <v>2.000453898087593</v>
+        <v>2.01689649100424</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.21291712253603</v>
+        <v>40.14194474835735</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1777,22 +1777,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.130335815518669</v>
+        <v>0.1301016063258892</v>
       </c>
       <c r="C5">
-        <v>18.98774527764274</v>
+        <v>18.84210085528978</v>
       </c>
       <c r="D5">
-        <v>19.45684527764274</v>
+        <v>19.51090085528978</v>
       </c>
       <c r="E5">
-        <v>-2.0709</v>
+        <v>-1.8712</v>
       </c>
       <c r="F5">
-        <v>0.5991</v>
+        <v>0.7988</v>
       </c>
       <c r="G5">
         <v>0.13</v>
@@ -1813,28 +1813,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M5">
-        <v>0.03013473</v>
+        <v>0.04017964</v>
       </c>
       <c r="N5">
-        <v>1.179531936666667</v>
+        <v>1.169487026666667</v>
       </c>
       <c r="O5">
-        <v>0.2429835789533334</v>
+        <v>0.2409143274933333</v>
       </c>
       <c r="P5">
-        <v>0.9365483577133334</v>
+        <v>0.9285726991733333</v>
       </c>
       <c r="Q5">
-        <v>1.093548357713333</v>
+        <v>1.085572699173333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1331316180604835</v>
+        <v>0.1338584149228013</v>
       </c>
       <c r="T5">
-        <v>2.01689649100424</v>
+        <v>2.033681637939984</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.14194474835735</v>
+        <v>30.10645856126801</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1859,22 +1859,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1301016063258892</v>
+        <v>0.1298673971331094</v>
       </c>
       <c r="C6">
-        <v>18.84210085528978</v>
+        <v>18.69675762730318</v>
       </c>
       <c r="D6">
-        <v>19.51090085528978</v>
+        <v>19.56525762730318</v>
       </c>
       <c r="E6">
-        <v>-1.8712</v>
+        <v>-1.6715</v>
       </c>
       <c r="F6">
-        <v>0.7988</v>
+        <v>0.9984999999999999</v>
       </c>
       <c r="G6">
         <v>0.13</v>
@@ -1895,28 +1895,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M6">
-        <v>0.04017964</v>
+        <v>0.05022454999999999</v>
       </c>
       <c r="N6">
-        <v>1.169487026666667</v>
+        <v>1.159442116666667</v>
       </c>
       <c r="O6">
-        <v>0.2409143274933333</v>
+        <v>0.2388450760333334</v>
       </c>
       <c r="P6">
-        <v>0.9285726991733333</v>
+        <v>0.9205970406333333</v>
       </c>
       <c r="Q6">
-        <v>1.085572699173333</v>
+        <v>1.077597040633333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1338584149228013</v>
+        <v>0.1346005127716941</v>
       </c>
       <c r="T6">
-        <v>2.033681637939984</v>
+        <v>2.050820156390164</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.10645856126801</v>
+        <v>24.08516684901441</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1298673971331094</v>
+        <v>0.1296331879403295</v>
       </c>
       <c r="C7">
-        <v>18.69675762730318</v>
+        <v>18.55171811807066</v>
       </c>
       <c r="D7">
-        <v>19.56525762730318</v>
+        <v>19.61991811807066</v>
       </c>
       <c r="E7">
-        <v>-1.6715</v>
+        <v>-1.4718</v>
       </c>
       <c r="F7">
-        <v>0.9984999999999999</v>
+        <v>1.1982</v>
       </c>
       <c r="G7">
         <v>0.13</v>
@@ -1977,28 +1977,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M7">
-        <v>0.05022454999999999</v>
+        <v>0.06026946</v>
       </c>
       <c r="N7">
-        <v>1.159442116666667</v>
+        <v>1.149397206666667</v>
       </c>
       <c r="O7">
-        <v>0.2388450760333334</v>
+        <v>0.2367758245733333</v>
       </c>
       <c r="P7">
-        <v>0.9205970406333333</v>
+        <v>0.9126213820933333</v>
       </c>
       <c r="Q7">
-        <v>1.077597040633333</v>
+        <v>1.069621382093333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1346005127716941</v>
+        <v>0.1353583999365208</v>
       </c>
       <c r="T7">
-        <v>2.050820156390164</v>
+        <v>2.068323324169071</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.08516684901441</v>
+        <v>20.07097237417868</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2023,22 +2023,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1296331879403295</v>
+        <v>0.1293989787475497</v>
       </c>
       <c r="C8">
-        <v>18.55171811807066</v>
+        <v>18.40698488026899</v>
       </c>
       <c r="D8">
-        <v>19.61991811807066</v>
+        <v>19.67488488026899</v>
       </c>
       <c r="E8">
-        <v>-1.4718</v>
+        <v>-1.2721</v>
       </c>
       <c r="F8">
-        <v>1.1982</v>
+        <v>1.3979</v>
       </c>
       <c r="G8">
         <v>0.13</v>
@@ -2059,28 +2059,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M8">
-        <v>0.06026946</v>
+        <v>0.07031436999999999</v>
       </c>
       <c r="N8">
-        <v>1.149397206666667</v>
+        <v>1.139352296666667</v>
       </c>
       <c r="O8">
-        <v>0.2367758245733333</v>
+        <v>0.2347065731133334</v>
       </c>
       <c r="P8">
-        <v>0.9126213820933333</v>
+        <v>0.9046457235533334</v>
       </c>
       <c r="Q8">
-        <v>1.069621382093333</v>
+        <v>1.061645723553333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1353583999365208</v>
+        <v>0.1361325857500534</v>
       </c>
       <c r="T8">
-        <v>2.068323324169071</v>
+        <v>2.086202904158279</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.07097237417868</v>
+        <v>17.20369060643887</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1293989787475497</v>
+        <v>0.1291647695547699</v>
       </c>
       <c r="C9">
-        <v>18.40698488026899</v>
+        <v>18.26256049526144</v>
       </c>
       <c r="D9">
-        <v>19.67488488026899</v>
+        <v>19.73016049526144</v>
       </c>
       <c r="E9">
-        <v>-1.2721</v>
+        <v>-1.0724</v>
       </c>
       <c r="F9">
-        <v>1.3979</v>
+        <v>1.5976</v>
       </c>
       <c r="G9">
         <v>0.13</v>
@@ -2141,28 +2141,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M9">
-        <v>0.07031437</v>
+        <v>0.08035927999999999</v>
       </c>
       <c r="N9">
-        <v>1.139352296666667</v>
+        <v>1.129307386666667</v>
       </c>
       <c r="O9">
-        <v>0.2347065731133334</v>
+        <v>0.2326373216533334</v>
       </c>
       <c r="P9">
-        <v>0.9046457235533334</v>
+        <v>0.8966700650133334</v>
       </c>
       <c r="Q9">
-        <v>1.061645723553333</v>
+        <v>1.053670065013333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1361325857500534</v>
+        <v>0.1369236016899672</v>
       </c>
       <c r="T9">
-        <v>2.086202904158279</v>
+        <v>2.10447117066899</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.20369060643887</v>
+        <v>15.05322928063401</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2187,22 +2187,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1291647695547699</v>
+        <v>0.12893056036199</v>
       </c>
       <c r="C10">
-        <v>18.26256049526144</v>
+        <v>18.11844757350185</v>
       </c>
       <c r="D10">
-        <v>19.73016049526144</v>
+        <v>19.78574757350185</v>
       </c>
       <c r="E10">
-        <v>-1.0724</v>
+        <v>-0.8727</v>
       </c>
       <c r="F10">
-        <v>1.5976</v>
+        <v>1.7973</v>
       </c>
       <c r="G10">
         <v>0.13</v>
@@ -2223,28 +2223,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M10">
-        <v>0.08035927999999999</v>
+        <v>0.09040419</v>
       </c>
       <c r="N10">
-        <v>1.129307386666667</v>
+        <v>1.119262476666667</v>
       </c>
       <c r="O10">
-        <v>0.2326373216533334</v>
+        <v>0.2305680701933333</v>
       </c>
       <c r="P10">
-        <v>0.8966700650133334</v>
+        <v>0.8886944064733332</v>
       </c>
       <c r="Q10">
-        <v>1.053670065013333</v>
+        <v>1.045694406473333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1369236016899672</v>
+        <v>0.1377320025955934</v>
       </c>
       <c r="T10">
-        <v>2.10447117066899</v>
+        <v>2.123140937542574</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.05322928063401</v>
+        <v>13.38064824945245</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2269,22 +2269,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.12893056036199</v>
+        <v>0.1288154511692102</v>
       </c>
       <c r="C11">
-        <v>18.11844757350185</v>
+        <v>17.9461824835054</v>
       </c>
       <c r="D11">
-        <v>19.78574757350185</v>
+        <v>19.8131824835054</v>
       </c>
       <c r="E11">
-        <v>-0.8727</v>
+        <v>-0.6730000000000003</v>
       </c>
       <c r="F11">
-        <v>1.7973</v>
+        <v>1.997</v>
       </c>
       <c r="G11">
         <v>0.13</v>
@@ -2305,45 +2305,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M11">
-        <v>0.09040419</v>
+        <v>0.1034446</v>
       </c>
       <c r="N11">
-        <v>1.119262476666667</v>
+        <v>1.106222066666667</v>
       </c>
       <c r="O11">
-        <v>0.2305680701933333</v>
+        <v>0.2278817457333334</v>
       </c>
       <c r="P11">
-        <v>0.8886944064733332</v>
+        <v>0.8783403209333334</v>
       </c>
       <c r="Q11">
-        <v>1.045694406473333</v>
+        <v>1.035340320933333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1377320025955934</v>
+        <v>0.1385583679657891</v>
       </c>
       <c r="T11">
-        <v>2.123140937542574</v>
+        <v>2.14222558812446</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.206</v>
       </c>
       <c r="W11">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.38064824945245</v>
+        <v>11.69385996626858</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2351,22 +2351,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1288154511692102</v>
+        <v>0.1285931519764304</v>
       </c>
       <c r="C12">
-        <v>17.9461824835054</v>
+        <v>17.79968077789739</v>
       </c>
       <c r="D12">
-        <v>19.8131824835054</v>
+        <v>19.86638077789739</v>
       </c>
       <c r="E12">
-        <v>-0.673</v>
+        <v>-0.4733000000000001</v>
       </c>
       <c r="F12">
-        <v>1.997</v>
+        <v>2.1967</v>
       </c>
       <c r="G12">
         <v>0.13</v>
@@ -2387,28 +2387,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M12">
-        <v>0.1034446</v>
+        <v>0.11378906</v>
       </c>
       <c r="N12">
-        <v>1.106222066666667</v>
+        <v>1.095877606666667</v>
       </c>
       <c r="O12">
-        <v>0.2278817457333334</v>
+        <v>0.2257507869733333</v>
       </c>
       <c r="P12">
-        <v>0.8783403209333334</v>
+        <v>0.8701268196933334</v>
       </c>
       <c r="Q12">
-        <v>1.035340320933333</v>
+        <v>1.027126819693333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1385583679657891</v>
+        <v>0.1394033033443038</v>
       </c>
       <c r="T12">
-        <v>2.14222558812446</v>
+        <v>2.161739107258748</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.69385996626858</v>
+        <v>10.63078178751689</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2433,22 +2433,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1285931519764304</v>
+        <v>0.1285328287836505</v>
       </c>
       <c r="C13">
-        <v>17.79968077789739</v>
+        <v>17.61446600141896</v>
       </c>
       <c r="D13">
-        <v>19.86638077789739</v>
+        <v>19.88086600141896</v>
       </c>
       <c r="E13">
-        <v>-0.4733000000000001</v>
+        <v>-0.2736000000000001</v>
       </c>
       <c r="F13">
-        <v>2.1967</v>
+        <v>2.3964</v>
       </c>
       <c r="G13">
         <v>0.13</v>
@@ -2469,45 +2469,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M13">
-        <v>0.11378906</v>
+        <v>0.1282074</v>
       </c>
       <c r="N13">
-        <v>1.095877606666667</v>
+        <v>1.081459266666667</v>
       </c>
       <c r="O13">
-        <v>0.2257507869733333</v>
+        <v>0.2227806089333333</v>
       </c>
       <c r="P13">
-        <v>0.8701268196933334</v>
+        <v>0.8586786577333334</v>
       </c>
       <c r="Q13">
-        <v>1.027126819693333</v>
+        <v>1.015678657733333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1394033033443038</v>
+        <v>0.1402674417996029</v>
       </c>
       <c r="T13">
-        <v>2.161739107258748</v>
+        <v>2.18169611546427</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.206</v>
       </c>
       <c r="W13">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.63078178751689</v>
+        <v>9.435232807674648</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1285328287836505</v>
+        <v>0.1283240275908707</v>
       </c>
       <c r="C14">
-        <v>17.61446600141896</v>
+        <v>17.46506830313371</v>
       </c>
       <c r="D14">
-        <v>19.88086600141896</v>
+        <v>19.93116830313371</v>
       </c>
       <c r="E14">
-        <v>-0.2736000000000001</v>
+        <v>-0.07390000000000008</v>
       </c>
       <c r="F14">
-        <v>2.3964</v>
+        <v>2.5961</v>
       </c>
       <c r="G14">
         <v>0.13</v>
@@ -2551,28 +2551,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M14">
-        <v>0.1282074</v>
+        <v>0.13889135</v>
       </c>
       <c r="N14">
-        <v>1.081459266666667</v>
+        <v>1.070775316666667</v>
       </c>
       <c r="O14">
-        <v>0.2227806089333333</v>
+        <v>0.2205797152333334</v>
       </c>
       <c r="P14">
-        <v>0.8586786577333334</v>
+        <v>0.8501956014333334</v>
       </c>
       <c r="Q14">
-        <v>1.015678657733333</v>
+        <v>1.007195601433333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1402674417996029</v>
+        <v>0.1411514455067479</v>
       </c>
       <c r="T14">
-        <v>2.18169611546427</v>
+        <v>2.202111905467619</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.435232807674648</v>
+        <v>8.709445668622752</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2597,22 +2597,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1283240275908707</v>
+        <v>0.1281152263980909</v>
       </c>
       <c r="C15">
-        <v>17.46506830313371</v>
+        <v>17.31592579896155</v>
       </c>
       <c r="D15">
-        <v>19.93116830313371</v>
+        <v>19.98172579896156</v>
       </c>
       <c r="E15">
-        <v>-0.07390000000000008</v>
+        <v>0.1258000000000004</v>
       </c>
       <c r="F15">
-        <v>2.5961</v>
+        <v>2.7958</v>
       </c>
       <c r="G15">
         <v>0.13</v>
@@ -2633,28 +2633,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M15">
-        <v>0.13889135</v>
+        <v>0.1495753</v>
       </c>
       <c r="N15">
-        <v>1.070775316666667</v>
+        <v>1.060091366666667</v>
       </c>
       <c r="O15">
-        <v>0.2205797152333334</v>
+        <v>0.2183788215333334</v>
       </c>
       <c r="P15">
-        <v>0.8501956014333334</v>
+        <v>0.8417125451333334</v>
       </c>
       <c r="Q15">
-        <v>1.007195601433333</v>
+        <v>0.9987125451333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1411514455067479</v>
+        <v>0.1420560074396405</v>
       </c>
       <c r="T15">
-        <v>2.202111905467619</v>
+        <v>2.223002481285001</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.709445668622752</v>
+        <v>8.087342406578269</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1281152263980909</v>
+        <v>0.128001705205311</v>
       </c>
       <c r="C16">
-        <v>17.31592579896155</v>
+        <v>17.14382071734959</v>
       </c>
       <c r="D16">
-        <v>19.98172579896156</v>
+        <v>20.0093207173496</v>
       </c>
       <c r="E16">
-        <v>0.1258000000000004</v>
+        <v>0.3255000000000003</v>
       </c>
       <c r="F16">
-        <v>2.7958</v>
+        <v>2.9955</v>
       </c>
       <c r="G16">
         <v>0.13</v>
@@ -2715,45 +2715,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M16">
-        <v>0.1495753</v>
+        <v>0.16265565</v>
       </c>
       <c r="N16">
-        <v>1.060091366666667</v>
+        <v>1.047011016666667</v>
       </c>
       <c r="O16">
-        <v>0.2183788215333334</v>
+        <v>0.2156842694333334</v>
       </c>
       <c r="P16">
-        <v>0.8417125451333334</v>
+        <v>0.8313267472333332</v>
       </c>
       <c r="Q16">
-        <v>0.9987125451333333</v>
+        <v>0.9883267472333331</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1420560074396405</v>
+        <v>0.1429818531827188</v>
       </c>
       <c r="T16">
-        <v>2.223002481285001</v>
+        <v>2.244384600062791</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.206</v>
       </c>
       <c r="W16">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.087342406578269</v>
+        <v>7.436979082292355</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2761,22 +2761,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.128001705205311</v>
+        <v>0.1277992560125312</v>
       </c>
       <c r="C17">
-        <v>17.14382071734959</v>
+        <v>16.99352202931615</v>
       </c>
       <c r="D17">
-        <v>20.0093207173496</v>
+        <v>20.05872202931615</v>
       </c>
       <c r="E17">
-        <v>0.3254999999999999</v>
+        <v>0.5251999999999999</v>
       </c>
       <c r="F17">
-        <v>2.9955</v>
+        <v>3.1952</v>
       </c>
       <c r="G17">
         <v>0.13</v>
@@ -2797,28 +2797,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M17">
-        <v>0.16265565</v>
+        <v>0.17349936</v>
       </c>
       <c r="N17">
-        <v>1.047011016666667</v>
+        <v>1.036167306666667</v>
       </c>
       <c r="O17">
-        <v>0.2156842694333334</v>
+        <v>0.2134504651733333</v>
       </c>
       <c r="P17">
-        <v>0.8313267472333332</v>
+        <v>0.8227168414933332</v>
       </c>
       <c r="Q17">
-        <v>0.9883267472333331</v>
+        <v>0.9797168414933332</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1429818531827188</v>
+        <v>0.1439297428720609</v>
       </c>
       <c r="T17">
-        <v>2.244384600062791</v>
+        <v>2.266275816906719</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.436979082292356</v>
+        <v>6.972167889649084</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2843,22 +2843,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1277992560125312</v>
+        <v>0.1275968068197513</v>
       </c>
       <c r="C18">
-        <v>16.99352202931615</v>
+        <v>16.84346788030858</v>
       </c>
       <c r="D18">
-        <v>20.05872202931615</v>
+        <v>20.10836788030858</v>
       </c>
       <c r="E18">
-        <v>0.5251999999999999</v>
+        <v>0.7249000000000003</v>
       </c>
       <c r="F18">
-        <v>3.1952</v>
+        <v>3.3949</v>
       </c>
       <c r="G18">
         <v>0.13</v>
@@ -2879,28 +2879,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M18">
-        <v>0.17349936</v>
+        <v>0.18434307</v>
       </c>
       <c r="N18">
-        <v>1.036167306666667</v>
+        <v>1.025323596666667</v>
       </c>
       <c r="O18">
-        <v>0.2134504651733333</v>
+        <v>0.2112166609133334</v>
       </c>
       <c r="P18">
-        <v>0.8227168414933332</v>
+        <v>0.8141069357533334</v>
       </c>
       <c r="Q18">
-        <v>0.9797168414933332</v>
+        <v>0.9711069357533333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1439297428720609</v>
+        <v>0.1449004732768088</v>
       </c>
       <c r="T18">
-        <v>2.266275816906719</v>
+        <v>2.288694532951705</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.972167889649084</v>
+        <v>6.562040366728549</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2925,22 +2925,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1275968068197513</v>
+        <v>0.1273943576269715</v>
       </c>
       <c r="C19">
-        <v>16.84346788030858</v>
+        <v>16.69366009055307</v>
       </c>
       <c r="D19">
-        <v>20.10836788030858</v>
+        <v>20.15826009055307</v>
       </c>
       <c r="E19">
-        <v>0.7249000000000003</v>
+        <v>0.9246000000000003</v>
       </c>
       <c r="F19">
-        <v>3.3949</v>
+        <v>3.5946</v>
       </c>
       <c r="G19">
         <v>0.13</v>
@@ -2961,28 +2961,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M19">
-        <v>0.18434307</v>
+        <v>0.19518678</v>
       </c>
       <c r="N19">
-        <v>1.025323596666667</v>
+        <v>1.014479886666667</v>
       </c>
       <c r="O19">
-        <v>0.2112166609133334</v>
+        <v>0.2089828566533334</v>
       </c>
       <c r="P19">
-        <v>0.8141069357533334</v>
+        <v>0.8054970300133333</v>
       </c>
       <c r="Q19">
-        <v>0.9711069357533333</v>
+        <v>0.9624970300133332</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1449004732768088</v>
+        <v>0.1458948800328921</v>
       </c>
       <c r="T19">
-        <v>2.288694532951705</v>
+        <v>2.311660046949009</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.562040366728549</v>
+        <v>6.197482568576963</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3007,22 +3007,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1273943576269715</v>
+        <v>0.1273427684341917</v>
       </c>
       <c r="C20">
-        <v>16.69366009055307</v>
+        <v>16.50671350064554</v>
       </c>
       <c r="D20">
-        <v>20.15826009055307</v>
+        <v>20.17101350064554</v>
       </c>
       <c r="E20">
-        <v>0.9245999999999999</v>
+        <v>1.1243</v>
       </c>
       <c r="F20">
-        <v>3.5946</v>
+        <v>3.7943</v>
       </c>
       <c r="G20">
         <v>0.13</v>
@@ -3043,45 +3043,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M20">
-        <v>0.19518678</v>
+        <v>0.20982479</v>
       </c>
       <c r="N20">
-        <v>1.014479886666667</v>
+        <v>0.9998418766666667</v>
       </c>
       <c r="O20">
-        <v>0.2089828566533334</v>
+        <v>0.2059674265933334</v>
       </c>
       <c r="P20">
-        <v>0.8054970300133333</v>
+        <v>0.7938744500733333</v>
       </c>
       <c r="Q20">
-        <v>0.9624970300133332</v>
+        <v>0.9508744500733333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1458948800328921</v>
+        <v>0.1469138400422119</v>
       </c>
       <c r="T20">
-        <v>2.311660046949009</v>
+        <v>2.335192610674641</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.206</v>
       </c>
       <c r="W20">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.197482568576963</v>
+        <v>5.765127498360259</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3089,22 +3089,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1273427684341917</v>
+        <v>0.1271482592414118</v>
       </c>
       <c r="C21">
-        <v>16.50671350064554</v>
+        <v>16.3552437589221</v>
       </c>
       <c r="D21">
-        <v>20.17101350064554</v>
+        <v>20.2192437589221</v>
       </c>
       <c r="E21">
-        <v>1.1243</v>
+        <v>1.324</v>
       </c>
       <c r="F21">
-        <v>3.7943</v>
+        <v>3.994</v>
       </c>
       <c r="G21">
         <v>0.13</v>
@@ -3125,28 +3125,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M21">
-        <v>0.20982479</v>
+        <v>0.2208682</v>
       </c>
       <c r="N21">
-        <v>0.9998418766666667</v>
+        <v>0.9887984666666667</v>
       </c>
       <c r="O21">
-        <v>0.2059674265933334</v>
+        <v>0.2036924841333334</v>
       </c>
       <c r="P21">
-        <v>0.7938744500733333</v>
+        <v>0.7851059825333333</v>
       </c>
       <c r="Q21">
-        <v>0.9508744500733333</v>
+        <v>0.9421059825333332</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1469138400422119</v>
+        <v>0.1479582740517648</v>
       </c>
       <c r="T21">
-        <v>2.335192610674641</v>
+        <v>2.359313488493413</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.765127498360259</v>
+        <v>5.476871123442247</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3171,22 +3171,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1271482592414118</v>
+        <v>0.126953750048632</v>
       </c>
       <c r="C22">
-        <v>16.3552437589221</v>
+        <v>16.20400521362765</v>
       </c>
       <c r="D22">
-        <v>20.2192437589221</v>
+        <v>20.26770521362765</v>
       </c>
       <c r="E22">
-        <v>1.324</v>
+        <v>1.5237</v>
       </c>
       <c r="F22">
-        <v>3.994</v>
+        <v>4.1937</v>
       </c>
       <c r="G22">
         <v>0.13</v>
@@ -3207,28 +3207,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M22">
-        <v>0.2208682</v>
+        <v>0.23191161</v>
       </c>
       <c r="N22">
-        <v>0.9887984666666667</v>
+        <v>0.9777550566666666</v>
       </c>
       <c r="O22">
-        <v>0.2036924841333334</v>
+        <v>0.2014175416733333</v>
       </c>
       <c r="P22">
-        <v>0.7851059825333333</v>
+        <v>0.7763375149933333</v>
       </c>
       <c r="Q22">
-        <v>0.9421059825333332</v>
+        <v>0.9333375149933332</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1479582740517648</v>
+        <v>0.1490291494286481</v>
       </c>
       <c r="T22">
-        <v>2.359313488493413</v>
+        <v>2.384045021446838</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.476871123442247</v>
+        <v>5.216067736611663</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3253,22 +3253,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.126953750048632</v>
+        <v>0.1267592408558522</v>
       </c>
       <c r="C23">
-        <v>16.20400521362765</v>
+        <v>16.05299953114999</v>
       </c>
       <c r="D23">
-        <v>20.26770521362765</v>
+        <v>20.31639953114999</v>
       </c>
       <c r="E23">
-        <v>1.5237</v>
+        <v>1.7234</v>
       </c>
       <c r="F23">
-        <v>4.1937</v>
+        <v>4.3934</v>
       </c>
       <c r="G23">
         <v>0.13</v>
@@ -3289,28 +3289,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M23">
-        <v>0.23191161</v>
+        <v>0.24295502</v>
       </c>
       <c r="N23">
-        <v>0.9777550566666666</v>
+        <v>0.9667116466666666</v>
       </c>
       <c r="O23">
-        <v>0.2014175416733333</v>
+        <v>0.1991425992133334</v>
       </c>
       <c r="P23">
-        <v>0.7763375149933333</v>
+        <v>0.7675690474533333</v>
       </c>
       <c r="Q23">
-        <v>0.9333375149933332</v>
+        <v>0.9245690474533332</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1490291494286481</v>
+        <v>0.1501274831485284</v>
       </c>
       <c r="T23">
-        <v>2.384045021446838</v>
+        <v>2.409410696270864</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.216067736611663</v>
+        <v>4.97897374858386</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3335,22 +3335,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1267592408558522</v>
+        <v>0.1265647316630723</v>
       </c>
       <c r="C24">
-        <v>16.05299953114999</v>
+        <v>15.90222839392987</v>
       </c>
       <c r="D24">
-        <v>20.31639953114999</v>
+        <v>20.36532839392988</v>
       </c>
       <c r="E24">
-        <v>1.7234</v>
+        <v>1.9231</v>
       </c>
       <c r="F24">
-        <v>4.3934</v>
+        <v>4.5931</v>
       </c>
       <c r="G24">
         <v>0.13</v>
@@ -3371,28 +3371,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M24">
-        <v>0.24295502</v>
+        <v>0.25399843</v>
       </c>
       <c r="N24">
-        <v>0.9667116466666666</v>
+        <v>0.9556682366666667</v>
       </c>
       <c r="O24">
-        <v>0.1991425992133334</v>
+        <v>0.1968676567533333</v>
       </c>
       <c r="P24">
-        <v>0.7675690474533333</v>
+        <v>0.7588005799133333</v>
       </c>
       <c r="Q24">
-        <v>0.9245690474533332</v>
+        <v>0.9158005799133332</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1501274831485284</v>
+        <v>0.151254345016977</v>
       </c>
       <c r="T24">
-        <v>2.409410696270864</v>
+        <v>2.435435219791617</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.97897374858386</v>
+        <v>4.762496629080214</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3417,22 +3417,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1265647316630723</v>
+        <v>0.1263702224702925</v>
       </c>
       <c r="C25">
-        <v>15.90222839392987</v>
+        <v>15.75169350065476</v>
       </c>
       <c r="D25">
-        <v>20.36532839392988</v>
+        <v>20.41449350065476</v>
       </c>
       <c r="E25">
-        <v>1.9231</v>
+        <v>2.1228</v>
       </c>
       <c r="F25">
-        <v>4.5931</v>
+        <v>4.7928</v>
       </c>
       <c r="G25">
         <v>0.13</v>
@@ -3453,28 +3453,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M25">
-        <v>0.25399843</v>
+        <v>0.26504184</v>
       </c>
       <c r="N25">
-        <v>0.9556682366666667</v>
+        <v>0.9446248266666667</v>
       </c>
       <c r="O25">
-        <v>0.1968676567533333</v>
+        <v>0.1945927142933334</v>
       </c>
       <c r="P25">
-        <v>0.7588005799133333</v>
+        <v>0.7500321123733333</v>
       </c>
       <c r="Q25">
-        <v>0.9158005799133332</v>
+        <v>0.9070321123733333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.151254345016977</v>
+        <v>0.1524108611451217</v>
       </c>
       <c r="T25">
-        <v>2.435435219791617</v>
+        <v>2.462144599194496</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.762496629080214</v>
+        <v>4.564059269535205</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3499,22 +3499,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1263702224702925</v>
+        <v>0.1266719632775126</v>
       </c>
       <c r="C26">
-        <v>15.75169350065476</v>
+        <v>15.47582512909266</v>
       </c>
       <c r="D26">
-        <v>20.41449350065476</v>
+        <v>20.33832512909266</v>
       </c>
       <c r="E26">
-        <v>2.1228</v>
+        <v>2.3225</v>
       </c>
       <c r="F26">
-        <v>4.7928</v>
+        <v>4.9925</v>
       </c>
       <c r="G26">
         <v>0.13</v>
@@ -3535,45 +3535,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M26">
-        <v>0.26504184</v>
+        <v>0.2885665</v>
       </c>
       <c r="N26">
-        <v>0.9446248266666667</v>
+        <v>0.9211001666666667</v>
       </c>
       <c r="O26">
-        <v>0.1945927142933334</v>
+        <v>0.1897466343333334</v>
       </c>
       <c r="P26">
-        <v>0.7500321123733333</v>
+        <v>0.7313535323333333</v>
       </c>
       <c r="Q26">
-        <v>0.9070321123733333</v>
+        <v>0.8883535323333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1524108611451217</v>
+        <v>0.1535982177033502</v>
       </c>
       <c r="T26">
-        <v>2.462144599194496</v>
+        <v>2.489566228714785</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.206</v>
       </c>
       <c r="W26">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.564059269535205</v>
+        <v>4.191985787216003</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3581,22 +3581,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1266719632775126</v>
+        <v>0.1264973040847328</v>
       </c>
       <c r="C27">
-        <v>15.47582512909266</v>
+        <v>15.32014488278617</v>
       </c>
       <c r="D27">
-        <v>20.33832512909266</v>
+        <v>20.38234488278617</v>
       </c>
       <c r="E27">
-        <v>2.3225</v>
+        <v>2.5222</v>
       </c>
       <c r="F27">
-        <v>4.9925</v>
+        <v>5.1922</v>
       </c>
       <c r="G27">
         <v>0.13</v>
@@ -3617,28 +3617,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M27">
-        <v>0.2885665</v>
+        <v>0.30010916</v>
       </c>
       <c r="N27">
-        <v>0.9211001666666667</v>
+        <v>0.9095575066666667</v>
       </c>
       <c r="O27">
-        <v>0.1897466343333334</v>
+        <v>0.1873688463733333</v>
       </c>
       <c r="P27">
-        <v>0.7313535323333333</v>
+        <v>0.7221886602933334</v>
       </c>
       <c r="Q27">
-        <v>0.8883535323333333</v>
+        <v>0.8791886602933333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1535982177033502</v>
+        <v>0.1548176649793686</v>
       </c>
       <c r="T27">
-        <v>2.489566228714785</v>
+        <v>2.517728983357244</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.191985787216003</v>
+        <v>4.030755564630772</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1264973040847328</v>
+        <v>0.127072974891953</v>
       </c>
       <c r="C28">
-        <v>15.32014488278617</v>
+        <v>14.97607314116712</v>
       </c>
       <c r="D28">
-        <v>20.38234488278617</v>
+        <v>20.23797314116712</v>
       </c>
       <c r="E28">
-        <v>2.5222</v>
+        <v>2.7219</v>
       </c>
       <c r="F28">
-        <v>5.1922</v>
+        <v>5.3919</v>
       </c>
       <c r="G28">
         <v>0.13</v>
@@ -3699,45 +3699,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M28">
-        <v>0.30010916</v>
+        <v>0.33052347</v>
       </c>
       <c r="N28">
-        <v>0.9095575066666667</v>
+        <v>0.8791431966666667</v>
       </c>
       <c r="O28">
-        <v>0.1873688463733333</v>
+        <v>0.1811034985133333</v>
       </c>
       <c r="P28">
-        <v>0.7221886602933334</v>
+        <v>0.6980396981533334</v>
       </c>
       <c r="Q28">
-        <v>0.8791886602933333</v>
+        <v>0.8550396981533334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1548176649793686</v>
+        <v>0.1560705217697986</v>
       </c>
       <c r="T28">
-        <v>2.517728983357244</v>
+        <v>2.546663320318674</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.206</v>
       </c>
       <c r="W28">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.030755564630772</v>
+        <v>3.659851043759969</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.127072974891953</v>
+        <v>0.1269261056991731</v>
       </c>
       <c r="C29">
-        <v>14.97607314116712</v>
+        <v>14.81301159130751</v>
       </c>
       <c r="D29">
-        <v>20.23797314116712</v>
+        <v>20.27461159130751</v>
       </c>
       <c r="E29">
-        <v>2.7219</v>
+        <v>2.921600000000001</v>
       </c>
       <c r="F29">
-        <v>5.3919</v>
+        <v>5.591600000000001</v>
       </c>
       <c r="G29">
         <v>0.13</v>
@@ -3781,28 +3781,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M29">
-        <v>0.33052347</v>
+        <v>0.3427650800000001</v>
       </c>
       <c r="N29">
-        <v>0.8791431966666667</v>
+        <v>0.8669015866666666</v>
       </c>
       <c r="O29">
-        <v>0.1811034985133333</v>
+        <v>0.1785817268533333</v>
       </c>
       <c r="P29">
-        <v>0.6980396981533334</v>
+        <v>0.6883198598133333</v>
       </c>
       <c r="Q29">
-        <v>0.8550396981533334</v>
+        <v>0.8453198598133332</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1560705217697986</v>
+        <v>0.1573581801377404</v>
       </c>
       <c r="T29">
-        <v>2.546663320318674</v>
+        <v>2.576401388862366</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.659851043759969</v>
+        <v>3.529142077911398</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3827,22 +3827,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1269261056991731</v>
+        <v>0.1274239645063933</v>
       </c>
       <c r="C30">
-        <v>14.81301159130751</v>
+        <v>14.4896482284123</v>
       </c>
       <c r="D30">
-        <v>20.27461159130751</v>
+        <v>20.1509482284123</v>
       </c>
       <c r="E30">
-        <v>2.921600000000001</v>
+        <v>3.121300000000001</v>
       </c>
       <c r="F30">
-        <v>5.591600000000001</v>
+        <v>5.791300000000001</v>
       </c>
       <c r="G30">
         <v>0.13</v>
@@ -3863,45 +3863,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M30">
-        <v>0.3427650800000001</v>
+        <v>0.37122233</v>
       </c>
       <c r="N30">
-        <v>0.8669015866666666</v>
+        <v>0.8384443366666666</v>
       </c>
       <c r="O30">
-        <v>0.1785817268533333</v>
+        <v>0.1727195333533333</v>
       </c>
       <c r="P30">
-        <v>0.6883198598133333</v>
+        <v>0.6657248033133333</v>
       </c>
       <c r="Q30">
-        <v>0.8453198598133332</v>
+        <v>0.8227248033133332</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1573581801377404</v>
+        <v>0.1586821105723849</v>
       </c>
       <c r="T30">
-        <v>2.576401388862366</v>
+        <v>2.606977149477712</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.206</v>
       </c>
       <c r="W30">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.529142077911398</v>
+        <v>3.258604261943689</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3909,22 +3909,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1274239645063933</v>
+        <v>0.1272993273136134</v>
       </c>
       <c r="C31">
-        <v>14.4896482284123</v>
+        <v>14.32076514067191</v>
       </c>
       <c r="D31">
-        <v>20.1509482284123</v>
+        <v>20.18176514067191</v>
       </c>
       <c r="E31">
-        <v>3.1213</v>
+        <v>3.321</v>
       </c>
       <c r="F31">
-        <v>5.7913</v>
+        <v>5.991</v>
       </c>
       <c r="G31">
         <v>0.13</v>
@@ -3945,28 +3945,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M31">
-        <v>0.37122233</v>
+        <v>0.3840231</v>
       </c>
       <c r="N31">
-        <v>0.8384443366666667</v>
+        <v>0.8256435666666666</v>
       </c>
       <c r="O31">
-        <v>0.1727195333533334</v>
+        <v>0.1700825747333333</v>
       </c>
       <c r="P31">
-        <v>0.6657248033133334</v>
+        <v>0.6555609919333333</v>
       </c>
       <c r="Q31">
-        <v>0.8227248033133333</v>
+        <v>0.8125609919333332</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1586821105723849</v>
+        <v>0.1600438675908764</v>
       </c>
       <c r="T31">
-        <v>2.606977149477712</v>
+        <v>2.638426503253496</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.258604261943689</v>
+        <v>3.1499841198789</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3991,22 +3991,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1272993273136134</v>
+        <v>0.1271746901208336</v>
       </c>
       <c r="C32">
-        <v>14.32076514067191</v>
+        <v>14.15197645411274</v>
       </c>
       <c r="D32">
-        <v>20.18176514067191</v>
+        <v>20.21267645411274</v>
       </c>
       <c r="E32">
-        <v>3.321</v>
+        <v>3.5207</v>
       </c>
       <c r="F32">
-        <v>5.991</v>
+        <v>6.1907</v>
       </c>
       <c r="G32">
         <v>0.13</v>
@@ -4027,28 +4027,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M32">
-        <v>0.3840231</v>
+        <v>0.39682387</v>
       </c>
       <c r="N32">
-        <v>0.8256435666666666</v>
+        <v>0.8128427966666667</v>
       </c>
       <c r="O32">
-        <v>0.1700825747333333</v>
+        <v>0.1674456161133334</v>
       </c>
       <c r="P32">
-        <v>0.6555609919333333</v>
+        <v>0.6453971805533334</v>
       </c>
       <c r="Q32">
-        <v>0.8125609919333332</v>
+        <v>0.8023971805533333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1600438675908764</v>
+        <v>0.1614450958272951</v>
       </c>
       <c r="T32">
-        <v>2.638426503253496</v>
+        <v>2.670787432501042</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.1499841198789</v>
+        <v>3.048371728915064</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4073,22 +4073,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1271746901208336</v>
+        <v>0.1290318769280538</v>
       </c>
       <c r="C33">
-        <v>14.15197645411274</v>
+        <v>13.50126276278824</v>
       </c>
       <c r="D33">
-        <v>20.21267645411274</v>
+        <v>19.76166276278824</v>
       </c>
       <c r="E33">
-        <v>3.5207</v>
+        <v>3.7204</v>
       </c>
       <c r="F33">
-        <v>6.1907</v>
+        <v>6.3904</v>
       </c>
       <c r="G33">
         <v>0.13</v>
@@ -4109,45 +4109,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M33">
-        <v>0.39682387</v>
+        <v>0.45946976</v>
       </c>
       <c r="N33">
-        <v>0.8128427966666667</v>
+        <v>0.7501969066666667</v>
       </c>
       <c r="O33">
-        <v>0.1674456161133334</v>
+        <v>0.1545405627733334</v>
       </c>
       <c r="P33">
-        <v>0.6453971805533334</v>
+        <v>0.5956563438933333</v>
       </c>
       <c r="Q33">
-        <v>0.8023971805533333</v>
+        <v>0.7526563438933332</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1614450958272951</v>
+        <v>0.1628875366589026</v>
       </c>
       <c r="T33">
-        <v>2.670787432501042</v>
+        <v>2.70410015378528</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.206</v>
       </c>
       <c r="W33">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.048371728915064</v>
+        <v>2.63274489852535</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4155,22 +4155,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1290318769280538</v>
+        <v>0.1289691717352739</v>
       </c>
       <c r="C34">
-        <v>13.50126276278824</v>
+        <v>13.31646201989681</v>
       </c>
       <c r="D34">
-        <v>19.76166276278824</v>
+        <v>19.77656201989682</v>
       </c>
       <c r="E34">
-        <v>3.7204</v>
+        <v>3.9201</v>
       </c>
       <c r="F34">
-        <v>6.3904</v>
+        <v>6.5901</v>
       </c>
       <c r="G34">
         <v>0.13</v>
@@ -4191,28 +4191,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M34">
-        <v>0.45946976</v>
+        <v>0.47382819</v>
       </c>
       <c r="N34">
-        <v>0.7501969066666667</v>
+        <v>0.7358384766666667</v>
       </c>
       <c r="O34">
-        <v>0.1545405627733334</v>
+        <v>0.1515827261933334</v>
       </c>
       <c r="P34">
-        <v>0.5956563438933333</v>
+        <v>0.5842557504733333</v>
       </c>
       <c r="Q34">
-        <v>0.7526563438933332</v>
+        <v>0.7412557504733333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1628875366589026</v>
+        <v>0.164373035425782</v>
       </c>
       <c r="T34">
-        <v>2.70410015378528</v>
+        <v>2.738407284660093</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.63274489852535</v>
+        <v>2.552964750085188</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4237,22 +4237,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1289691717352739</v>
+        <v>0.1299593105424941</v>
       </c>
       <c r="C35">
-        <v>13.31646201989681</v>
+        <v>12.88408970588815</v>
       </c>
       <c r="D35">
-        <v>19.77656201989682</v>
+        <v>19.54388970588815</v>
       </c>
       <c r="E35">
-        <v>3.9201</v>
+        <v>4.119800000000001</v>
       </c>
       <c r="F35">
-        <v>6.5901</v>
+        <v>6.789800000000001</v>
       </c>
       <c r="G35">
         <v>0.13</v>
@@ -4273,45 +4273,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M35">
-        <v>0.47382819</v>
+        <v>0.5146668400000001</v>
       </c>
       <c r="N35">
-        <v>0.7358384766666667</v>
+        <v>0.6949998266666666</v>
       </c>
       <c r="O35">
-        <v>0.1515827261933334</v>
+        <v>0.1431699642933333</v>
       </c>
       <c r="P35">
-        <v>0.5842557504733333</v>
+        <v>0.5518298623733333</v>
       </c>
       <c r="Q35">
-        <v>0.7412557504733333</v>
+        <v>0.7088298623733332</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.164373035425782</v>
+        <v>0.1659035493068092</v>
       </c>
       <c r="T35">
-        <v>2.738407284660093</v>
+        <v>2.773754025561415</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.206</v>
       </c>
       <c r="W35">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.552964750085188</v>
+        <v>2.350387809454882</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4319,22 +4319,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1299593105424941</v>
+        <v>0.1299275713497142</v>
       </c>
       <c r="C36">
-        <v>12.88408970588815</v>
+        <v>12.6917631183508</v>
       </c>
       <c r="D36">
-        <v>19.54388970588815</v>
+        <v>19.5512631183508</v>
       </c>
       <c r="E36">
-        <v>4.119800000000001</v>
+        <v>4.319500000000001</v>
       </c>
       <c r="F36">
-        <v>6.789800000000001</v>
+        <v>6.9895</v>
       </c>
       <c r="G36">
         <v>0.13</v>
@@ -4355,28 +4355,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M36">
-        <v>0.5146668400000001</v>
+        <v>0.5298041000000001</v>
       </c>
       <c r="N36">
-        <v>0.6949998266666666</v>
+        <v>0.6798625666666666</v>
       </c>
       <c r="O36">
-        <v>0.1431699642933333</v>
+        <v>0.1400516887333333</v>
       </c>
       <c r="P36">
-        <v>0.5518298623733333</v>
+        <v>0.5398108779333333</v>
       </c>
       <c r="Q36">
-        <v>0.7088298623733332</v>
+        <v>0.6968108779333332</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1659035493068092</v>
+        <v>0.1674811559226373</v>
       </c>
       <c r="T36">
-        <v>2.773754025561415</v>
+        <v>2.81018835849047</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.350387809454882</v>
+        <v>2.283233872041886</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4401,22 +4401,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1299275713497142</v>
+        <v>0.1298958321569344</v>
       </c>
       <c r="C37">
-        <v>12.6917631183508</v>
+        <v>12.4994420965152</v>
       </c>
       <c r="D37">
-        <v>19.5512631183508</v>
+        <v>19.5586420965152</v>
       </c>
       <c r="E37">
-        <v>4.319500000000001</v>
+        <v>4.519200000000001</v>
       </c>
       <c r="F37">
-        <v>6.9895</v>
+        <v>7.1892</v>
       </c>
       <c r="G37">
         <v>0.13</v>
@@ -4437,28 +4437,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M37">
-        <v>0.5298041000000001</v>
+        <v>0.54494136</v>
       </c>
       <c r="N37">
-        <v>0.6798625666666666</v>
+        <v>0.6647253066666666</v>
       </c>
       <c r="O37">
-        <v>0.1400516887333333</v>
+        <v>0.1369334131733333</v>
       </c>
       <c r="P37">
-        <v>0.5398108779333333</v>
+        <v>0.5277918934933333</v>
       </c>
       <c r="Q37">
-        <v>0.6968108779333332</v>
+        <v>0.6847918934933332</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1674811559226373</v>
+        <v>0.16910806274521</v>
       </c>
       <c r="T37">
-        <v>2.81018835849047</v>
+        <v>2.847761264323558</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.283233872041886</v>
+        <v>2.219810708929611</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4483,22 +4483,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1298958321569344</v>
+        <v>0.1298640929641546</v>
       </c>
       <c r="C38">
-        <v>12.49944209651519</v>
+        <v>12.30712664668548</v>
       </c>
       <c r="D38">
-        <v>19.55864209651519</v>
+        <v>19.56602664668548</v>
       </c>
       <c r="E38">
-        <v>4.5192</v>
+        <v>4.7189</v>
       </c>
       <c r="F38">
-        <v>7.1892</v>
+        <v>7.3889</v>
       </c>
       <c r="G38">
         <v>0.13</v>
@@ -4519,28 +4519,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M38">
-        <v>0.54494136</v>
+        <v>0.56007862</v>
       </c>
       <c r="N38">
-        <v>0.6647253066666666</v>
+        <v>0.6495880466666667</v>
       </c>
       <c r="O38">
-        <v>0.1369334131733333</v>
+        <v>0.1338151376133334</v>
       </c>
       <c r="P38">
-        <v>0.5277918934933333</v>
+        <v>0.5157729090533334</v>
       </c>
       <c r="Q38">
-        <v>0.6847918934933332</v>
+        <v>0.6727729090533333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.16910806274521</v>
+        <v>0.17078661740342</v>
       </c>
       <c r="T38">
-        <v>2.847761264323558</v>
+        <v>2.886526960818014</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.219810708929611</v>
+        <v>2.159815824904487</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4565,22 +4565,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1298640929641546</v>
+        <v>0.1298323537713748</v>
       </c>
       <c r="C39">
-        <v>12.30712664668548</v>
+        <v>12.11481677517532</v>
       </c>
       <c r="D39">
-        <v>19.56602664668548</v>
+        <v>19.57341677517532</v>
       </c>
       <c r="E39">
-        <v>4.7189</v>
+        <v>4.9186</v>
       </c>
       <c r="F39">
-        <v>7.3889</v>
+        <v>7.5886</v>
       </c>
       <c r="G39">
         <v>0.13</v>
@@ -4601,28 +4601,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M39">
-        <v>0.56007862</v>
+        <v>0.57521588</v>
       </c>
       <c r="N39">
-        <v>0.6495880466666667</v>
+        <v>0.6344507866666667</v>
       </c>
       <c r="O39">
-        <v>0.1338151376133334</v>
+        <v>0.1306968620533333</v>
       </c>
       <c r="P39">
-        <v>0.5157729090533334</v>
+        <v>0.5037539246133333</v>
       </c>
       <c r="Q39">
-        <v>0.6727729090533333</v>
+        <v>0.6607539246133333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.17078661740342</v>
+        <v>0.1725193189860883</v>
       </c>
       <c r="T39">
-        <v>2.886526960818014</v>
+        <v>2.926543163651</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.159815824904487</v>
+        <v>2.102978566354369</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4647,22 +4647,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1298323537713748</v>
+        <v>0.1298006145785949</v>
       </c>
       <c r="C40">
-        <v>12.11481677517532</v>
+        <v>11.92251248830795</v>
       </c>
       <c r="D40">
-        <v>19.57341677517532</v>
+        <v>19.58081248830795</v>
       </c>
       <c r="E40">
-        <v>4.9186</v>
+        <v>5.1183</v>
       </c>
       <c r="F40">
-        <v>7.5886</v>
+        <v>7.7883</v>
       </c>
       <c r="G40">
         <v>0.13</v>
@@ -4683,28 +4683,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M40">
-        <v>0.57521588</v>
+        <v>0.5903531400000001</v>
       </c>
       <c r="N40">
-        <v>0.6344507866666667</v>
+        <v>0.6193135266666666</v>
       </c>
       <c r="O40">
-        <v>0.1306968620533333</v>
+        <v>0.1275785864933333</v>
       </c>
       <c r="P40">
-        <v>0.5037539246133333</v>
+        <v>0.4917349401733333</v>
       </c>
       <c r="Q40">
-        <v>0.6607539246133333</v>
+        <v>0.6487349401733332</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1725193189860883</v>
+        <v>0.174308830456713</v>
       </c>
       <c r="T40">
-        <v>2.926543163651</v>
+        <v>2.967871373134249</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.102978566354369</v>
+        <v>2.049056039011949</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4729,22 +4729,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1298006145785949</v>
+        <v>0.1342787953858151</v>
       </c>
       <c r="C41">
-        <v>11.92251248830795</v>
+        <v>10.73176804322302</v>
       </c>
       <c r="D41">
-        <v>19.58081248830795</v>
+        <v>18.58976804322302</v>
       </c>
       <c r="E41">
-        <v>5.1183</v>
+        <v>5.318</v>
       </c>
       <c r="F41">
-        <v>7.7883</v>
+        <v>7.988</v>
       </c>
       <c r="G41">
         <v>0.13</v>
@@ -4765,45 +4765,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M41">
-        <v>0.5903531400000001</v>
+        <v>0.7189199999999999</v>
       </c>
       <c r="N41">
-        <v>0.6193135266666666</v>
+        <v>0.4907466666666668</v>
       </c>
       <c r="O41">
-        <v>0.1275785864933333</v>
+        <v>0.1010938133333334</v>
       </c>
       <c r="P41">
-        <v>0.4917349401733333</v>
+        <v>0.3896528533333334</v>
       </c>
       <c r="Q41">
-        <v>0.6487349401733332</v>
+        <v>0.5466528533333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.174308830456713</v>
+        <v>0.1761579923096918</v>
       </c>
       <c r="T41">
-        <v>2.967871373134249</v>
+        <v>3.010577189600273</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.206</v>
       </c>
       <c r="W41">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.049056039011949</v>
+        <v>1.682616517368646</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1342787953858151</v>
+        <v>0.1343598041930353</v>
       </c>
       <c r="C42">
-        <v>10.73176804322302</v>
+        <v>10.51506332026317</v>
       </c>
       <c r="D42">
-        <v>18.58976804322302</v>
+        <v>18.57276332026317</v>
       </c>
       <c r="E42">
-        <v>5.318</v>
+        <v>5.5177</v>
       </c>
       <c r="F42">
-        <v>7.988</v>
+        <v>8.1877</v>
       </c>
       <c r="G42">
         <v>0.13</v>
@@ -4847,28 +4847,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M42">
-        <v>0.7189199999999999</v>
+        <v>0.7368929999999999</v>
       </c>
       <c r="N42">
-        <v>0.4907466666666668</v>
+        <v>0.4727736666666668</v>
       </c>
       <c r="O42">
-        <v>0.1010938133333334</v>
+        <v>0.09739137533333336</v>
       </c>
       <c r="P42">
-        <v>0.3896528533333334</v>
+        <v>0.3753822913333334</v>
       </c>
       <c r="Q42">
-        <v>0.5466528533333334</v>
+        <v>0.5323822913333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1761579923096918</v>
+        <v>0.178069837615314</v>
       </c>
       <c r="T42">
-        <v>3.010577189600273</v>
+        <v>3.054730660861755</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.682616517368646</v>
+        <v>1.641577090115752</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4893,22 +4893,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1343598041930353</v>
+        <v>0.1344408130002554</v>
       </c>
       <c r="C43">
-        <v>10.51506332026317</v>
+        <v>10.29838967852376</v>
       </c>
       <c r="D43">
-        <v>18.57276332026317</v>
+        <v>18.55578967852376</v>
       </c>
       <c r="E43">
-        <v>5.5177</v>
+        <v>5.7174</v>
       </c>
       <c r="F43">
-        <v>8.1877</v>
+        <v>8.3874</v>
       </c>
       <c r="G43">
         <v>0.13</v>
@@ -4929,28 +4929,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M43">
-        <v>0.7368929999999999</v>
+        <v>0.7548659999999999</v>
       </c>
       <c r="N43">
-        <v>0.4727736666666668</v>
+        <v>0.4548006666666667</v>
       </c>
       <c r="O43">
-        <v>0.09739137533333336</v>
+        <v>0.09368893733333336</v>
       </c>
       <c r="P43">
-        <v>0.3753822913333334</v>
+        <v>0.3611117293333334</v>
       </c>
       <c r="Q43">
-        <v>0.5323822913333334</v>
+        <v>0.5181117293333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.178069837615314</v>
+        <v>0.18004760862113</v>
       </c>
       <c r="T43">
-        <v>3.054730660861755</v>
+        <v>3.100406665615012</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.641577090115752</v>
+        <v>1.602491921303472</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4975,22 +4975,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1344408130002554</v>
+        <v>0.1345218218074755</v>
       </c>
       <c r="C44">
-        <v>10.29838967852376</v>
+        <v>10.08174703286723</v>
       </c>
       <c r="D44">
-        <v>18.55578967852376</v>
+        <v>18.53884703286723</v>
       </c>
       <c r="E44">
-        <v>5.7174</v>
+        <v>5.9171</v>
       </c>
       <c r="F44">
-        <v>8.3874</v>
+        <v>8.5871</v>
       </c>
       <c r="G44">
         <v>0.13</v>
@@ -5011,28 +5011,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M44">
-        <v>0.7548659999999999</v>
+        <v>0.7728389999999999</v>
       </c>
       <c r="N44">
-        <v>0.4548006666666667</v>
+        <v>0.4368276666666667</v>
       </c>
       <c r="O44">
-        <v>0.09368893733333336</v>
+        <v>0.08998649933333336</v>
       </c>
       <c r="P44">
-        <v>0.3611117293333334</v>
+        <v>0.3468411673333334</v>
       </c>
       <c r="Q44">
-        <v>0.5181117293333333</v>
+        <v>0.5038411673333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.18004760862113</v>
+        <v>0.1820947751008343</v>
       </c>
       <c r="T44">
-        <v>3.100406665615012</v>
+        <v>3.147685337201716</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.602491921303472</v>
+        <v>1.56522466731967</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5057,22 +5057,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1345218218074755</v>
+        <v>0.1346028306146957</v>
       </c>
       <c r="C45">
-        <v>10.08174703286723</v>
+        <v>9.865135298466715</v>
       </c>
       <c r="D45">
-        <v>18.53884703286723</v>
+        <v>18.52193529846672</v>
       </c>
       <c r="E45">
-        <v>5.9171</v>
+        <v>6.1168</v>
       </c>
       <c r="F45">
-        <v>8.5871</v>
+        <v>8.786799999999999</v>
       </c>
       <c r="G45">
         <v>0.13</v>
@@ -5093,28 +5093,28 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M45">
-        <v>0.7728389999999999</v>
+        <v>0.790812</v>
       </c>
       <c r="N45">
-        <v>0.4368276666666667</v>
+        <v>0.4188546666666667</v>
       </c>
       <c r="O45">
-        <v>0.08998649933333336</v>
+        <v>0.08628406133333334</v>
       </c>
       <c r="P45">
-        <v>0.3468411673333334</v>
+        <v>0.3325706053333334</v>
       </c>
       <c r="Q45">
-        <v>0.5038411673333333</v>
+        <v>0.4895706053333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1820947751008343</v>
+        <v>0.1842150546690995</v>
       </c>
       <c r="T45">
-        <v>3.147685337201716</v>
+        <v>3.196652532773661</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.56522466731967</v>
+        <v>1.529651379426042</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5139,22 +5139,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1346028306146957</v>
+        <v>0.1567647263843598</v>
       </c>
       <c r="C46">
-        <v>9.865135298466715</v>
+        <v>5.966230939459376</v>
       </c>
       <c r="D46">
-        <v>18.52193529846672</v>
+        <v>14.82273093945937</v>
       </c>
       <c r="E46">
-        <v>6.1168</v>
+        <v>6.3165</v>
       </c>
       <c r="F46">
-        <v>8.786799999999999</v>
+        <v>8.986499999999999</v>
       </c>
       <c r="G46">
         <v>0.13</v>
@@ -5175,45 +5175,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M46">
-        <v>0.790812</v>
+        <v>1.3192182</v>
       </c>
       <c r="N46">
-        <v>0.4188546666666667</v>
+        <v>-0.1095515333333335</v>
       </c>
       <c r="O46">
-        <v>0.08628406133333334</v>
+        <v>-0.02256761586666669</v>
       </c>
       <c r="P46">
-        <v>0.3325706053333334</v>
+        <v>-0.08698391746666675</v>
       </c>
       <c r="Q46">
-        <v>0.4895706053333333</v>
+        <v>0.07001608253333316</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1842150546690995</v>
+        <v>0.1876054735948466</v>
       </c>
       <c r="T46">
-        <v>3.196652532773661</v>
+        <v>3.274953200804773</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.206</v>
+        <v>0.1888931894157717</v>
       </c>
       <c r="W46">
-        <v>0.07146</v>
+        <v>0.1190704797937647</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.529651379426042</v>
+        <v>0.9169572301736487</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5221,22 +5221,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1567647263843598</v>
+        <v>0.1577747263843598</v>
       </c>
       <c r="C47">
-        <v>5.966230939459376</v>
+        <v>5.632831499127942</v>
       </c>
       <c r="D47">
-        <v>14.82273093945937</v>
+        <v>14.68903149912794</v>
       </c>
       <c r="E47">
-        <v>6.3165</v>
+        <v>6.5162</v>
       </c>
       <c r="F47">
-        <v>8.986499999999999</v>
+        <v>9.186199999999999</v>
       </c>
       <c r="G47">
         <v>0.13</v>
@@ -5257,37 +5257,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M47">
-        <v>1.3192182</v>
+        <v>1.34853416</v>
       </c>
       <c r="N47">
-        <v>-0.1095515333333335</v>
+        <v>-0.1388674933333334</v>
       </c>
       <c r="O47">
-        <v>-0.02256761586666669</v>
+        <v>-0.02860670362666668</v>
       </c>
       <c r="P47">
-        <v>-0.08698391746666675</v>
+        <v>-0.1102607897066667</v>
       </c>
       <c r="Q47">
-        <v>0.07001608253333316</v>
+        <v>0.04673921029333322</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1876054735948466</v>
+        <v>0.1902315008836401</v>
       </c>
       <c r="T47">
-        <v>3.274953200804773</v>
+        <v>3.335600482301158</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1888931894157717</v>
+        <v>0.1847868157328201</v>
       </c>
       <c r="W47">
-        <v>0.1190704797937647</v>
+        <v>0.119673295450422</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9169572301736487</v>
+        <v>0.8970233773437869</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5303,22 +5303,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1577747263843598</v>
+        <v>0.1587847263843598</v>
       </c>
       <c r="C48">
-        <v>5.632831499127942</v>
+        <v>5.301822407280879</v>
       </c>
       <c r="D48">
-        <v>14.68903149912794</v>
+        <v>14.55772240728088</v>
       </c>
       <c r="E48">
-        <v>6.5162</v>
+        <v>6.7159</v>
       </c>
       <c r="F48">
-        <v>9.186199999999999</v>
+        <v>9.385899999999999</v>
       </c>
       <c r="G48">
         <v>0.13</v>
@@ -5339,37 +5339,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M48">
-        <v>1.34853416</v>
+        <v>1.37785012</v>
       </c>
       <c r="N48">
-        <v>-0.1388674933333334</v>
+        <v>-0.1681834533333333</v>
       </c>
       <c r="O48">
-        <v>-0.02860670362666668</v>
+        <v>-0.03464579138666666</v>
       </c>
       <c r="P48">
-        <v>-0.1102607897066667</v>
+        <v>-0.1335376619466666</v>
       </c>
       <c r="Q48">
-        <v>0.04673921029333322</v>
+        <v>0.02346233805333328</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1902315008836401</v>
+        <v>0.192956623541822</v>
       </c>
       <c r="T48">
-        <v>3.335600482301158</v>
+        <v>3.398536340457783</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1847868157328201</v>
+        <v>0.1808551813555261</v>
       </c>
       <c r="W48">
-        <v>0.119673295450422</v>
+        <v>0.1202504593770088</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8970233773437869</v>
+        <v>0.8779377735705148</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5385,22 +5385,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1587847263843598</v>
+        <v>0.1597947263843598</v>
       </c>
       <c r="C49">
-        <v>5.301822407280879</v>
+        <v>4.973140128032471</v>
       </c>
       <c r="D49">
-        <v>14.55772240728088</v>
+        <v>14.42874012803247</v>
       </c>
       <c r="E49">
-        <v>6.7159</v>
+        <v>6.9156</v>
       </c>
       <c r="F49">
-        <v>9.385899999999999</v>
+        <v>9.585599999999999</v>
       </c>
       <c r="G49">
         <v>0.13</v>
@@ -5421,37 +5421,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M49">
-        <v>1.37785012</v>
+        <v>1.40716608</v>
       </c>
       <c r="N49">
-        <v>-0.1681834533333333</v>
+        <v>-0.1974994133333334</v>
       </c>
       <c r="O49">
-        <v>-0.03464579138666666</v>
+        <v>-0.04068487914666669</v>
       </c>
       <c r="P49">
-        <v>-0.1335376619466666</v>
+        <v>-0.1568145341866667</v>
       </c>
       <c r="Q49">
-        <v>0.02346233805333328</v>
+        <v>0.0001854658133331744</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.192956623541822</v>
+        <v>0.195786558609934</v>
       </c>
       <c r="T49">
-        <v>3.398536340457783</v>
+        <v>3.46389280854351</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1808551813555261</v>
+        <v>0.1770873650772859</v>
       </c>
       <c r="W49">
-        <v>0.1202504593770088</v>
+        <v>0.1208035748066544</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8779377735705148</v>
+        <v>0.8596474032877957</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5467,22 +5467,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1597947263843598</v>
+        <v>0.1608047263843598</v>
       </c>
       <c r="C50">
-        <v>4.973140128032473</v>
+        <v>4.646723357448558</v>
       </c>
       <c r="D50">
-        <v>14.42874012803247</v>
+        <v>14.30202335744856</v>
       </c>
       <c r="E50">
-        <v>6.9156</v>
+        <v>7.1153</v>
       </c>
       <c r="F50">
-        <v>9.585599999999999</v>
+        <v>9.785299999999999</v>
       </c>
       <c r="G50">
         <v>0.13</v>
@@ -5503,37 +5503,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M50">
-        <v>1.40716608</v>
+        <v>1.43648204</v>
       </c>
       <c r="N50">
-        <v>-0.1974994133333334</v>
+        <v>-0.2268153733333333</v>
       </c>
       <c r="O50">
-        <v>-0.04068487914666669</v>
+        <v>-0.04672396690666667</v>
       </c>
       <c r="P50">
-        <v>-0.1568145341866667</v>
+        <v>-0.1800914064266667</v>
       </c>
       <c r="Q50">
-        <v>0.0001854658133331744</v>
+        <v>-0.02309140642666677</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1957865586099339</v>
+        <v>0.1987274715238542</v>
       </c>
       <c r="T50">
-        <v>3.463892808543509</v>
+        <v>3.531812275377696</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1770873650772859</v>
+        <v>0.1734733372185658</v>
       </c>
       <c r="W50">
-        <v>0.1208035748066544</v>
+        <v>0.1213341140963145</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8596474032877957</v>
+        <v>0.8421035787309019</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5549,22 +5549,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1608047263843598</v>
+        <v>0.1618147263843598</v>
       </c>
       <c r="C51">
-        <v>4.646723357448558</v>
+        <v>4.322512926392015</v>
       </c>
       <c r="D51">
-        <v>14.30202335744856</v>
+        <v>14.17751292639201</v>
       </c>
       <c r="E51">
-        <v>7.1153</v>
+        <v>7.315</v>
       </c>
       <c r="F51">
-        <v>9.785299999999999</v>
+        <v>9.984999999999999</v>
       </c>
       <c r="G51">
         <v>0.13</v>
@@ -5585,37 +5585,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M51">
-        <v>1.43648204</v>
+        <v>1.465798</v>
       </c>
       <c r="N51">
-        <v>-0.2268153733333333</v>
+        <v>-0.2561313333333335</v>
       </c>
       <c r="O51">
-        <v>-0.04672396690666667</v>
+        <v>-0.0527630546666667</v>
       </c>
       <c r="P51">
-        <v>-0.1800914064266667</v>
+        <v>-0.2033682786666668</v>
       </c>
       <c r="Q51">
-        <v>-0.02309140642666677</v>
+        <v>-0.04636827866666687</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1987274715238542</v>
+        <v>0.2017860209543313</v>
       </c>
       <c r="T51">
-        <v>3.531812275377696</v>
+        <v>3.60244852088525</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1734733372185658</v>
+        <v>0.1700038704741945</v>
       </c>
       <c r="W51">
-        <v>0.1213341140963145</v>
+        <v>0.1218434318143883</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8421035787309019</v>
+        <v>0.8252615071562839</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5631,22 +5631,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1618147263843598</v>
+        <v>0.1628247263843598</v>
       </c>
       <c r="C52">
-        <v>4.322512926392015</v>
+        <v>4.000451708399293</v>
       </c>
       <c r="D52">
-        <v>14.17751292639201</v>
+        <v>14.05515170839929</v>
       </c>
       <c r="E52">
-        <v>7.315</v>
+        <v>7.514699999999999</v>
       </c>
       <c r="F52">
-        <v>9.984999999999999</v>
+        <v>10.1847</v>
       </c>
       <c r="G52">
         <v>0.13</v>
@@ -5667,37 +5667,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M52">
-        <v>1.465798</v>
+        <v>1.49511396</v>
       </c>
       <c r="N52">
-        <v>-0.2561313333333335</v>
+        <v>-0.2854472933333334</v>
       </c>
       <c r="O52">
-        <v>-0.0527630546666667</v>
+        <v>-0.05880214242666669</v>
       </c>
       <c r="P52">
-        <v>-0.2033682786666668</v>
+        <v>-0.2266451509066667</v>
       </c>
       <c r="Q52">
-        <v>-0.04636827866666687</v>
+        <v>-0.06964515090666679</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2017860209543313</v>
+        <v>0.2049694091370728</v>
       </c>
       <c r="T52">
-        <v>3.60244852088525</v>
+        <v>3.675967878454337</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1700038704741945</v>
+        <v>0.1666704612492103</v>
       </c>
       <c r="W52">
-        <v>0.1218434318143883</v>
+        <v>0.1223327762886159</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8252615071562839</v>
+        <v>0.8090799089767489</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5713,22 +5713,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1628247263843598</v>
+        <v>0.1938631993000546</v>
       </c>
       <c r="C53">
-        <v>4.000451708399293</v>
+        <v>0.8543717322172419</v>
       </c>
       <c r="D53">
-        <v>14.05515170839929</v>
+        <v>11.10877173221724</v>
       </c>
       <c r="E53">
-        <v>7.514699999999999</v>
+        <v>7.714399999999999</v>
       </c>
       <c r="F53">
-        <v>10.1847</v>
+        <v>10.3844</v>
       </c>
       <c r="G53">
         <v>0.13</v>
@@ -5749,45 +5749,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M53">
-        <v>1.49511396</v>
+        <v>2.08518752</v>
       </c>
       <c r="N53">
-        <v>-0.2854472933333334</v>
+        <v>-0.8755208533333332</v>
       </c>
       <c r="O53">
-        <v>-0.05880214242666669</v>
+        <v>-0.1803572957866666</v>
       </c>
       <c r="P53">
-        <v>-0.2266451509066667</v>
+        <v>-0.6951635575466666</v>
       </c>
       <c r="Q53">
-        <v>-0.06964515090666679</v>
+        <v>-0.5381635575466667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2049694091370728</v>
+        <v>0.2123447570684593</v>
       </c>
       <c r="T53">
-        <v>3.675967878454337</v>
+        <v>3.846299239456336</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1666704612492103</v>
+        <v>0.1195054789764584</v>
       </c>
       <c r="W53">
-        <v>0.1223327762886159</v>
+        <v>0.1768032998215272</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8090799089767489</v>
+        <v>0.5801236843517397</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1938631993000546</v>
+        <v>0.1954131993000546</v>
       </c>
       <c r="C54">
-        <v>0.8543717322172419</v>
+        <v>0.5395843183694549</v>
       </c>
       <c r="D54">
-        <v>11.10877173221724</v>
+        <v>10.99368431836945</v>
       </c>
       <c r="E54">
-        <v>7.714399999999999</v>
+        <v>7.914099999999999</v>
       </c>
       <c r="F54">
-        <v>10.3844</v>
+        <v>10.5841</v>
       </c>
       <c r="G54">
         <v>0.13</v>
@@ -5831,37 +5831,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M54">
-        <v>2.08518752</v>
+        <v>2.12528728</v>
       </c>
       <c r="N54">
-        <v>-0.8755208533333332</v>
+        <v>-0.9156206133333331</v>
       </c>
       <c r="O54">
-        <v>-0.1803572957866666</v>
+        <v>-0.1886178463466666</v>
       </c>
       <c r="P54">
-        <v>-0.6951635575466666</v>
+        <v>-0.7270027669866664</v>
       </c>
       <c r="Q54">
-        <v>-0.5381635575466667</v>
+        <v>-0.5700027669866665</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2123447570684593</v>
+        <v>0.215888262538001</v>
       </c>
       <c r="T54">
-        <v>3.846299239456336</v>
+        <v>3.928135393487322</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1195054789764584</v>
+        <v>0.117250658618412</v>
       </c>
       <c r="W54">
-        <v>0.1768032998215272</v>
+        <v>0.1772560677494229</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5801236843517397</v>
+        <v>0.5691779544583107</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1954131993000546</v>
+        <v>0.1969631993000546</v>
       </c>
       <c r="C55">
-        <v>0.5395843183694549</v>
+        <v>0.2271570754136576</v>
       </c>
       <c r="D55">
-        <v>10.99368431836945</v>
+        <v>10.88095707541366</v>
       </c>
       <c r="E55">
-        <v>7.914099999999999</v>
+        <v>8.113799999999999</v>
       </c>
       <c r="F55">
-        <v>10.5841</v>
+        <v>10.7838</v>
       </c>
       <c r="G55">
         <v>0.13</v>
@@ -5913,37 +5913,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M55">
-        <v>2.12528728</v>
+        <v>2.16538704</v>
       </c>
       <c r="N55">
-        <v>-0.9156206133333331</v>
+        <v>-0.9557203733333335</v>
       </c>
       <c r="O55">
-        <v>-0.1886178463466666</v>
+        <v>-0.1968783969066667</v>
       </c>
       <c r="P55">
-        <v>-0.7270027669866664</v>
+        <v>-0.7588419764266667</v>
       </c>
       <c r="Q55">
-        <v>-0.5700027669866665</v>
+        <v>-0.6018419764266668</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.215888262538001</v>
+        <v>0.2195858334627402</v>
       </c>
       <c r="T55">
-        <v>3.928135393487322</v>
+        <v>4.013529641171829</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.117250658618412</v>
+        <v>0.1150793501254784</v>
       </c>
       <c r="W55">
-        <v>0.1772560677494229</v>
+        <v>0.1776920664948039</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5691779544583107</v>
+        <v>0.5586376219683418</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5959,22 +5959,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1969631993000546</v>
+        <v>0.1985131993000546</v>
       </c>
       <c r="C56">
-        <v>0.2271570754136576</v>
+        <v>-0.08298186204684299</v>
       </c>
       <c r="D56">
-        <v>10.88095707541366</v>
+        <v>10.77051813795316</v>
       </c>
       <c r="E56">
-        <v>8.113799999999999</v>
+        <v>8.313499999999999</v>
       </c>
       <c r="F56">
-        <v>10.7838</v>
+        <v>10.9835</v>
       </c>
       <c r="G56">
         <v>0.13</v>
@@ -5995,37 +5995,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M56">
-        <v>2.16538704</v>
+        <v>2.2054868</v>
       </c>
       <c r="N56">
-        <v>-0.9557203733333335</v>
+        <v>-0.9958201333333334</v>
       </c>
       <c r="O56">
-        <v>-0.1968783969066667</v>
+        <v>-0.2051389474666667</v>
       </c>
       <c r="P56">
-        <v>-0.7588419764266667</v>
+        <v>-0.7906811858666667</v>
       </c>
       <c r="Q56">
-        <v>-0.6018419764266668</v>
+        <v>-0.6336811858666668</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2195858334627402</v>
+        <v>0.2234477408730233</v>
       </c>
       <c r="T56">
-        <v>4.013529641171829</v>
+        <v>4.102719188753425</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1150793501254784</v>
+        <v>0.1129869983050152</v>
       </c>
       <c r="W56">
-        <v>0.1776920664948039</v>
+        <v>0.178112210740353</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5586376219683418</v>
+        <v>0.5484805742961901</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6041,22 +6041,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1985131993000546</v>
+        <v>0.2000631993000546</v>
       </c>
       <c r="C57">
-        <v>-0.08298186204684299</v>
+        <v>-0.3909014710629606</v>
       </c>
       <c r="D57">
-        <v>10.77051813795316</v>
+        <v>10.66229852893704</v>
       </c>
       <c r="E57">
-        <v>8.313499999999999</v>
+        <v>8.513200000000001</v>
       </c>
       <c r="F57">
-        <v>10.9835</v>
+        <v>11.1832</v>
       </c>
       <c r="G57">
         <v>0.13</v>
@@ -6077,37 +6077,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M57">
-        <v>2.2054868</v>
+        <v>2.24558656</v>
       </c>
       <c r="N57">
-        <v>-0.9958201333333334</v>
+        <v>-1.035919893333334</v>
       </c>
       <c r="O57">
-        <v>-0.2051389474666667</v>
+        <v>-0.2133994980266668</v>
       </c>
       <c r="P57">
-        <v>-0.7906811858666667</v>
+        <v>-0.822520395306667</v>
       </c>
       <c r="Q57">
-        <v>-0.6336811858666668</v>
+        <v>-0.6655203953066671</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2234477408730233</v>
+        <v>0.2274851895292284</v>
       </c>
       <c r="T57">
-        <v>4.102719188753425</v>
+        <v>4.195962806679639</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1129869983050152</v>
+        <v>0.1109693733352827</v>
       </c>
       <c r="W57">
-        <v>0.178112210740353</v>
+        <v>0.1785173498342752</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5484805742961901</v>
+        <v>0.5386862783266152</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6123,22 +6123,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2000631993000546</v>
+        <v>0.2016131993000546</v>
       </c>
       <c r="C58">
-        <v>-0.3909014710629606</v>
+        <v>-0.6966679840034118</v>
       </c>
       <c r="D58">
-        <v>10.66229852893704</v>
+        <v>10.55623201599659</v>
       </c>
       <c r="E58">
-        <v>8.513200000000001</v>
+        <v>8.712900000000001</v>
       </c>
       <c r="F58">
-        <v>11.1832</v>
+        <v>11.3829</v>
       </c>
       <c r="G58">
         <v>0.13</v>
@@ -6159,37 +6159,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M58">
-        <v>2.24558656</v>
+        <v>2.28568632</v>
       </c>
       <c r="N58">
-        <v>-1.035919893333334</v>
+        <v>-1.076019653333334</v>
       </c>
       <c r="O58">
-        <v>-0.2133994980266668</v>
+        <v>-0.2216600485866668</v>
       </c>
       <c r="P58">
-        <v>-0.822520395306667</v>
+        <v>-0.8543596047466669</v>
       </c>
       <c r="Q58">
-        <v>-0.6655203953066671</v>
+        <v>-0.697359604746667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2274851895292284</v>
+        <v>0.2317104264950243</v>
       </c>
       <c r="T58">
-        <v>4.195962806679639</v>
+        <v>4.293543337067537</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1109693733352827</v>
+        <v>0.1090225422241374</v>
       </c>
       <c r="W58">
-        <v>0.1785173498342752</v>
+        <v>0.1789082735213932</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5386862783266152</v>
+        <v>0.5292356418647448</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6205,22 +6205,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2016131993000546</v>
+        <v>0.2031631993000546</v>
       </c>
       <c r="C59">
-        <v>-0.6966679840034118</v>
+        <v>-1.000345023727903</v>
       </c>
       <c r="D59">
-        <v>10.55623201599659</v>
+        <v>10.4522549762721</v>
       </c>
       <c r="E59">
-        <v>8.712900000000001</v>
+        <v>8.912600000000001</v>
       </c>
       <c r="F59">
-        <v>11.3829</v>
+        <v>11.5826</v>
       </c>
       <c r="G59">
         <v>0.13</v>
@@ -6241,37 +6241,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M59">
-        <v>2.28568632</v>
+        <v>2.32578608</v>
       </c>
       <c r="N59">
-        <v>-1.076019653333334</v>
+        <v>-1.116119413333334</v>
       </c>
       <c r="O59">
-        <v>-0.2216600485866668</v>
+        <v>-0.2299205991466667</v>
       </c>
       <c r="P59">
-        <v>-0.8543596047466669</v>
+        <v>-0.8861988141866669</v>
       </c>
       <c r="Q59">
-        <v>-0.697359604746667</v>
+        <v>-0.729198814186667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2317104264950243</v>
+        <v>0.2361368652210964</v>
       </c>
       <c r="T59">
-        <v>4.293543337067537</v>
+        <v>4.39577055937867</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1090225422241374</v>
+        <v>0.107142843220273</v>
       </c>
       <c r="W59">
-        <v>0.1789082735213932</v>
+        <v>0.1792857170813692</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5292356418647448</v>
+        <v>0.5201108894188009</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6287,22 +6287,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2031631993000546</v>
+        <v>0.2047131993000546</v>
       </c>
       <c r="C60">
-        <v>-1.000345023727901</v>
+        <v>-1.301993730849652</v>
       </c>
       <c r="D60">
-        <v>10.4522549762721</v>
+        <v>10.35030626915035</v>
       </c>
       <c r="E60">
-        <v>8.912599999999999</v>
+        <v>9.112299999999999</v>
       </c>
       <c r="F60">
-        <v>11.5826</v>
+        <v>11.7823</v>
       </c>
       <c r="G60">
         <v>0.13</v>
@@ -6323,37 +6323,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M60">
-        <v>2.32578608</v>
+        <v>2.36588584</v>
       </c>
       <c r="N60">
-        <v>-1.116119413333333</v>
+        <v>-1.156219173333333</v>
       </c>
       <c r="O60">
-        <v>-0.2299205991466667</v>
+        <v>-0.2381811497066667</v>
       </c>
       <c r="P60">
-        <v>-0.8861988141866666</v>
+        <v>-0.9180380236266665</v>
       </c>
       <c r="Q60">
-        <v>-0.7291988141866667</v>
+        <v>-0.7610380236266666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2361368652210963</v>
+        <v>0.2407792277874646</v>
       </c>
       <c r="T60">
-        <v>4.395770559378668</v>
+        <v>4.502984475461075</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.107142843220273</v>
+        <v>0.1053268628267091</v>
       </c>
       <c r="W60">
-        <v>0.1792857170813692</v>
+        <v>0.1796503659443968</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.520110889418801</v>
+        <v>0.5112954506150926</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6369,22 +6369,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2047131993000546</v>
+        <v>0.2062631993000546</v>
       </c>
       <c r="C61">
-        <v>-1.301993730849652</v>
+        <v>-1.601672883622145</v>
       </c>
       <c r="D61">
-        <v>10.35030626915035</v>
+        <v>10.25032711637785</v>
       </c>
       <c r="E61">
-        <v>9.112299999999999</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="F61">
-        <v>11.7823</v>
+        <v>11.982</v>
       </c>
       <c r="G61">
         <v>0.13</v>
@@ -6405,37 +6405,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M61">
-        <v>2.36588584</v>
+        <v>2.4059856</v>
       </c>
       <c r="N61">
-        <v>-1.156219173333333</v>
+        <v>-1.196318933333333</v>
       </c>
       <c r="O61">
-        <v>-0.2381811497066667</v>
+        <v>-0.2464417002666666</v>
       </c>
       <c r="P61">
-        <v>-0.9180380236266665</v>
+        <v>-0.9498772330666665</v>
       </c>
       <c r="Q61">
-        <v>-0.7610380236266666</v>
+        <v>-0.7928772330666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2407792277874646</v>
+        <v>0.2456537084821512</v>
       </c>
       <c r="T61">
-        <v>4.502984475461075</v>
+        <v>4.615559087347602</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1053268628267091</v>
+        <v>0.1035714151129306</v>
       </c>
       <c r="W61">
-        <v>0.1796503659443968</v>
+        <v>0.1800028598453235</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5112954506150926</v>
+        <v>0.5027738597715077</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6451,22 +6451,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2062631993000546</v>
+        <v>0.2299494316564803</v>
       </c>
       <c r="C62">
-        <v>-1.601672883622145</v>
+        <v>-3.119821860759419</v>
       </c>
       <c r="D62">
-        <v>10.25032711637785</v>
+        <v>8.931878139240579</v>
       </c>
       <c r="E62">
-        <v>9.311999999999999</v>
+        <v>9.511699999999999</v>
       </c>
       <c r="F62">
-        <v>11.982</v>
+        <v>12.1817</v>
       </c>
       <c r="G62">
         <v>0.13</v>
@@ -6487,45 +6487,45 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M62">
-        <v>2.4059856</v>
+        <v>2.87244486</v>
       </c>
       <c r="N62">
-        <v>-1.196318933333333</v>
+        <v>-1.662778193333333</v>
       </c>
       <c r="O62">
-        <v>-0.2464417002666666</v>
+        <v>-0.3425323078266667</v>
       </c>
       <c r="P62">
-        <v>-0.9498772330666665</v>
+        <v>-1.320245885506667</v>
       </c>
       <c r="Q62">
-        <v>-0.7928772330666666</v>
+        <v>-1.163245885506667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2456537084821512</v>
+        <v>0.2527941429468876</v>
       </c>
       <c r="T62">
-        <v>4.615559087347602</v>
+        <v>4.780465195078238</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1035714151129306</v>
+        <v>0.08675234703489952</v>
       </c>
       <c r="W62">
-        <v>0.1800028598453235</v>
+        <v>0.2153437965691707</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5027738597715077</v>
+        <v>0.4211278982276675</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6533,22 +6533,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2299494316564803</v>
+        <v>0.2318494316564803</v>
       </c>
       <c r="C63">
-        <v>-3.119821860759419</v>
+        <v>-3.410737234617111</v>
       </c>
       <c r="D63">
-        <v>8.931878139240579</v>
+        <v>8.840662765382888</v>
       </c>
       <c r="E63">
-        <v>9.511699999999999</v>
+        <v>9.711399999999999</v>
       </c>
       <c r="F63">
-        <v>12.1817</v>
+        <v>12.3814</v>
       </c>
       <c r="G63">
         <v>0.13</v>
@@ -6569,37 +6569,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M63">
-        <v>2.87244486</v>
+        <v>2.91953412</v>
       </c>
       <c r="N63">
-        <v>-1.662778193333333</v>
+        <v>-1.709867453333333</v>
       </c>
       <c r="O63">
-        <v>-0.3425323078266667</v>
+        <v>-0.3522326953866666</v>
       </c>
       <c r="P63">
-        <v>-1.320245885506667</v>
+        <v>-1.357634757946667</v>
       </c>
       <c r="Q63">
-        <v>-1.163245885506667</v>
+        <v>-1.200634757946667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2527941429468876</v>
+        <v>0.2582413572349636</v>
       </c>
       <c r="T63">
-        <v>4.780465195078238</v>
+        <v>4.906266910738191</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08675234703489952</v>
+        <v>0.08535311563111081</v>
       </c>
       <c r="W63">
-        <v>0.2153437965691707</v>
+        <v>0.2156737353341841</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4211278982276675</v>
+        <v>0.4143355127723826</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6615,22 +6615,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2318494316564803</v>
+        <v>0.2337494316564803</v>
       </c>
       <c r="C64">
-        <v>-3.410737234617111</v>
+        <v>-3.699808397414392</v>
       </c>
       <c r="D64">
-        <v>8.840662765382888</v>
+        <v>8.751291602585606</v>
       </c>
       <c r="E64">
-        <v>9.711399999999999</v>
+        <v>9.911099999999999</v>
       </c>
       <c r="F64">
-        <v>12.3814</v>
+        <v>12.5811</v>
       </c>
       <c r="G64">
         <v>0.13</v>
@@ -6651,37 +6651,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M64">
-        <v>2.91953412</v>
+        <v>2.96662338</v>
       </c>
       <c r="N64">
-        <v>-1.709867453333333</v>
+        <v>-1.756956713333333</v>
       </c>
       <c r="O64">
-        <v>-0.3522326953866666</v>
+        <v>-0.3619330829466667</v>
       </c>
       <c r="P64">
-        <v>-1.357634757946667</v>
+        <v>-1.395023630386667</v>
       </c>
       <c r="Q64">
-        <v>-1.200634757946667</v>
+        <v>-1.238023630386667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2582413572349636</v>
+        <v>0.2639830155386113</v>
       </c>
       <c r="T64">
-        <v>4.906266910738191</v>
+        <v>5.03886871913652</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08535311563111081</v>
+        <v>0.08399830427188683</v>
       </c>
       <c r="W64">
-        <v>0.2156737353341841</v>
+        <v>0.2159931998526891</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4143355127723826</v>
+        <v>0.4077587586013923</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6697,22 +6697,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2337494316564803</v>
+        <v>0.2356494316564803</v>
       </c>
       <c r="C65">
-        <v>-3.699808397414392</v>
+        <v>-3.987090719362024</v>
       </c>
       <c r="D65">
-        <v>8.751291602585606</v>
+        <v>8.663709280637974</v>
       </c>
       <c r="E65">
-        <v>9.911099999999999</v>
+        <v>10.1108</v>
       </c>
       <c r="F65">
-        <v>12.5811</v>
+        <v>12.7808</v>
       </c>
       <c r="G65">
         <v>0.13</v>
@@ -6733,37 +6733,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M65">
-        <v>2.96662338</v>
+        <v>3.01371264</v>
       </c>
       <c r="N65">
-        <v>-1.756956713333333</v>
+        <v>-1.804045973333333</v>
       </c>
       <c r="O65">
-        <v>-0.3619330829466667</v>
+        <v>-0.3716334705066667</v>
       </c>
       <c r="P65">
-        <v>-1.395023630386667</v>
+        <v>-1.432412502826667</v>
       </c>
       <c r="Q65">
-        <v>-1.238023630386667</v>
+        <v>-1.275412502826667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2639830155386113</v>
+        <v>0.2700436548591283</v>
       </c>
       <c r="T65">
-        <v>5.03886871913652</v>
+        <v>5.178837294668091</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08399830427188683</v>
+        <v>0.08268583076763861</v>
       </c>
       <c r="W65">
-        <v>0.2159931998526891</v>
+        <v>0.2163026811049908</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4077587586013923</v>
+        <v>0.4013875279982456</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6779,22 +6779,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2356494316564803</v>
+        <v>0.2375494316564803</v>
       </c>
       <c r="C66">
-        <v>-3.987090719362024</v>
+        <v>-4.272637376069209</v>
       </c>
       <c r="D66">
-        <v>8.663709280637974</v>
+        <v>8.577862623930789</v>
       </c>
       <c r="E66">
-        <v>10.1108</v>
+        <v>10.3105</v>
       </c>
       <c r="F66">
-        <v>12.7808</v>
+        <v>12.9805</v>
       </c>
       <c r="G66">
         <v>0.13</v>
@@ -6815,37 +6815,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M66">
-        <v>3.01371264</v>
+        <v>3.0608019</v>
       </c>
       <c r="N66">
-        <v>-1.804045973333333</v>
+        <v>-1.851135233333333</v>
       </c>
       <c r="O66">
-        <v>-0.3716334705066667</v>
+        <v>-0.3813338580666667</v>
       </c>
       <c r="P66">
-        <v>-1.432412502826667</v>
+        <v>-1.469801375266667</v>
       </c>
       <c r="Q66">
-        <v>-1.275412502826667</v>
+        <v>-1.312801375266667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2700436548591283</v>
+        <v>0.276450616426532</v>
       </c>
       <c r="T66">
-        <v>5.178837294668091</v>
+        <v>5.326804074515751</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08268583076763861</v>
+        <v>0.08141374106352108</v>
       </c>
       <c r="W66">
-        <v>0.2163026811049908</v>
+        <v>0.2166026398572218</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4013875279982456</v>
+        <v>0.395212335259811</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6861,22 +6861,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2375494316564803</v>
+        <v>0.2394494316564803</v>
       </c>
       <c r="C67">
-        <v>-4.272637376069209</v>
+        <v>-4.556499456205753</v>
       </c>
       <c r="D67">
-        <v>8.577862623930789</v>
+        <v>8.493700543794246</v>
       </c>
       <c r="E67">
-        <v>10.3105</v>
+        <v>10.5102</v>
       </c>
       <c r="F67">
-        <v>12.9805</v>
+        <v>13.1802</v>
       </c>
       <c r="G67">
         <v>0.13</v>
@@ -6897,37 +6897,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M67">
-        <v>3.0608019</v>
+        <v>3.10789116</v>
       </c>
       <c r="N67">
-        <v>-1.851135233333333</v>
+        <v>-1.898224493333333</v>
       </c>
       <c r="O67">
-        <v>-0.3813338580666667</v>
+        <v>-0.3910342456266667</v>
       </c>
       <c r="P67">
-        <v>-1.469801375266667</v>
+        <v>-1.507190247706667</v>
       </c>
       <c r="Q67">
-        <v>-1.312801375266667</v>
+        <v>-1.350190247706667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.276450616426532</v>
+        <v>0.2832344580861358</v>
       </c>
       <c r="T67">
-        <v>5.326804074515751</v>
+        <v>5.483474782589743</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08141374106352108</v>
+        <v>0.08018019953225562</v>
       </c>
       <c r="W67">
-        <v>0.2166026398572218</v>
+        <v>0.2168935089502941</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.395212335259811</v>
+        <v>0.3892242695740563</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2394494316564803</v>
+        <v>0.2413494316564803</v>
       </c>
       <c r="C68">
-        <v>-4.556499456205753</v>
+        <v>-4.838726062887783</v>
       </c>
       <c r="D68">
-        <v>8.493700543794246</v>
+        <v>8.411173937112215</v>
       </c>
       <c r="E68">
-        <v>10.5102</v>
+        <v>10.7099</v>
       </c>
       <c r="F68">
-        <v>13.1802</v>
+        <v>13.3799</v>
       </c>
       <c r="G68">
         <v>0.13</v>
@@ -6979,37 +6979,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M68">
-        <v>3.10789116</v>
+        <v>3.15498042</v>
       </c>
       <c r="N68">
-        <v>-1.898224493333333</v>
+        <v>-1.945313753333333</v>
       </c>
       <c r="O68">
-        <v>-0.3910342456266667</v>
+        <v>-0.4007346331866666</v>
       </c>
       <c r="P68">
-        <v>-1.507190247706667</v>
+        <v>-1.544579120146667</v>
       </c>
       <c r="Q68">
-        <v>-1.350190247706667</v>
+        <v>-1.387579120146667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2832344580861358</v>
+        <v>0.2904294416645036</v>
       </c>
       <c r="T68">
-        <v>5.483474782589743</v>
+        <v>5.649640685092463</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08018019953225562</v>
+        <v>0.07898348013625181</v>
       </c>
       <c r="W68">
-        <v>0.2168935089502941</v>
+        <v>0.2171756953838718</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3892242695740563</v>
+        <v>0.3834149521177271</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7025,22 +7025,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2413494316564803</v>
+        <v>0.2432494316564803</v>
       </c>
       <c r="C69">
-        <v>-4.838726062887783</v>
+        <v>-5.119364409209881</v>
       </c>
       <c r="D69">
-        <v>8.411173937112215</v>
+        <v>8.330235590790119</v>
       </c>
       <c r="E69">
-        <v>10.7099</v>
+        <v>10.9096</v>
       </c>
       <c r="F69">
-        <v>13.3799</v>
+        <v>13.5796</v>
       </c>
       <c r="G69">
         <v>0.13</v>
@@ -7061,37 +7061,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M69">
-        <v>3.15498042</v>
+        <v>3.202069680000001</v>
       </c>
       <c r="N69">
-        <v>-1.945313753333333</v>
+        <v>-1.992403013333334</v>
       </c>
       <c r="O69">
-        <v>-0.4007346331866666</v>
+        <v>-0.4104350207466668</v>
       </c>
       <c r="P69">
-        <v>-1.544579120146667</v>
+        <v>-1.581967992586667</v>
       </c>
       <c r="Q69">
-        <v>-1.387579120146667</v>
+        <v>-1.424967992586667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2904294416645036</v>
+        <v>0.2980741117165194</v>
       </c>
       <c r="T69">
-        <v>5.649640685092463</v>
+        <v>5.826191956501603</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07898348013625181</v>
+        <v>0.0778219583695422</v>
       </c>
       <c r="W69">
-        <v>0.2171756953838718</v>
+        <v>0.217449582216462</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3834149521177271</v>
+        <v>0.3777764969395252</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7107,22 +7107,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2432494316564803</v>
+        <v>0.2451494316564803</v>
       </c>
       <c r="C70">
-        <v>-5.119364409209881</v>
+        <v>-5.398459908314063</v>
       </c>
       <c r="D70">
-        <v>8.330235590790119</v>
+        <v>8.250840091685937</v>
       </c>
       <c r="E70">
-        <v>10.9096</v>
+        <v>11.1093</v>
       </c>
       <c r="F70">
-        <v>13.5796</v>
+        <v>13.7793</v>
       </c>
       <c r="G70">
         <v>0.13</v>
@@ -7143,37 +7143,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M70">
-        <v>3.202069680000001</v>
+        <v>3.24915894</v>
       </c>
       <c r="N70">
-        <v>-1.992403013333334</v>
+        <v>-2.039492273333334</v>
       </c>
       <c r="O70">
-        <v>-0.4104350207466668</v>
+        <v>-0.4201354083066668</v>
       </c>
       <c r="P70">
-        <v>-1.581967992586667</v>
+        <v>-1.619356865026667</v>
       </c>
       <c r="Q70">
-        <v>-1.424967992586667</v>
+        <v>-1.462356865026667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2980741117165194</v>
+        <v>0.30621198628802</v>
       </c>
       <c r="T70">
-        <v>5.826191956501603</v>
+        <v>6.014133632517783</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0778219583695422</v>
+        <v>0.07669410390041841</v>
       </c>
       <c r="W70">
-        <v>0.217449582216462</v>
+        <v>0.2177155303002813</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3777764969395252</v>
+        <v>0.3723014752447494</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7189,22 +7189,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2451494316564803</v>
+        <v>0.2470494316564803</v>
       </c>
       <c r="C71">
-        <v>-5.398459908314063</v>
+        <v>-5.676056258356741</v>
       </c>
       <c r="D71">
-        <v>8.250840091685937</v>
+        <v>8.172943741643259</v>
       </c>
       <c r="E71">
-        <v>11.1093</v>
+        <v>11.309</v>
       </c>
       <c r="F71">
-        <v>13.7793</v>
+        <v>13.979</v>
       </c>
       <c r="G71">
         <v>0.13</v>
@@ -7225,37 +7225,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M71">
-        <v>3.24915894</v>
+        <v>3.2962482</v>
       </c>
       <c r="N71">
-        <v>-2.039492273333334</v>
+        <v>-2.086581533333334</v>
       </c>
       <c r="O71">
-        <v>-0.4201354083066668</v>
+        <v>-0.4298357958666668</v>
       </c>
       <c r="P71">
-        <v>-1.619356865026667</v>
+        <v>-1.656745737466667</v>
       </c>
       <c r="Q71">
-        <v>-1.462356865026667</v>
+        <v>-1.499745737466667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.30621198628802</v>
+        <v>0.3148923858309539</v>
       </c>
       <c r="T71">
-        <v>6.014133632517783</v>
+        <v>6.214604753601709</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07669410390041841</v>
+        <v>0.07559847384469814</v>
       </c>
       <c r="W71">
-        <v>0.2177155303002813</v>
+        <v>0.2179738798674202</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3723014752447494</v>
+        <v>0.3669828827412531</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7271,22 +7271,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2470494316564803</v>
+        <v>0.2489494316564803</v>
       </c>
       <c r="C72">
-        <v>-5.676056258356741</v>
+        <v>-5.95219552270763</v>
       </c>
       <c r="D72">
-        <v>8.172943741643259</v>
+        <v>8.09650447729237</v>
       </c>
       <c r="E72">
-        <v>11.309</v>
+        <v>11.5087</v>
       </c>
       <c r="F72">
-        <v>13.979</v>
+        <v>14.1787</v>
       </c>
       <c r="G72">
         <v>0.13</v>
@@ -7307,37 +7307,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M72">
-        <v>3.2962482</v>
+        <v>3.34333746</v>
       </c>
       <c r="N72">
-        <v>-2.086581533333334</v>
+        <v>-2.133670793333334</v>
       </c>
       <c r="O72">
-        <v>-0.4298357958666668</v>
+        <v>-0.4395361834266668</v>
       </c>
       <c r="P72">
-        <v>-1.656745737466667</v>
+        <v>-1.694134609906667</v>
       </c>
       <c r="Q72">
-        <v>-1.499745737466667</v>
+        <v>-1.537134609906667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3148923858309539</v>
+        <v>0.3241714336182283</v>
       </c>
       <c r="T72">
-        <v>6.214604753601709</v>
+        <v>6.428901469243149</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07559847384469814</v>
+        <v>0.07453370660744887</v>
       </c>
       <c r="W72">
-        <v>0.2179738798674202</v>
+        <v>0.2182249519819636</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3669828827412531</v>
+        <v>0.3618141097448974</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7353,22 +7353,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2489494316564803</v>
+        <v>0.2508494316564803</v>
       </c>
       <c r="C73">
-        <v>-5.952195522707626</v>
+        <v>-6.226918205689882</v>
       </c>
       <c r="D73">
-        <v>8.096504477292372</v>
+        <v>8.021481794310116</v>
       </c>
       <c r="E73">
-        <v>11.5087</v>
+        <v>11.7084</v>
       </c>
       <c r="F73">
-        <v>14.1787</v>
+        <v>14.3784</v>
       </c>
       <c r="G73">
         <v>0.13</v>
@@ -7389,37 +7389,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M73">
-        <v>3.34333746</v>
+        <v>3.39042672</v>
       </c>
       <c r="N73">
-        <v>-2.133670793333333</v>
+        <v>-2.180760053333333</v>
       </c>
       <c r="O73">
-        <v>-0.4395361834266667</v>
+        <v>-0.4492365709866666</v>
       </c>
       <c r="P73">
-        <v>-1.694134609906667</v>
+        <v>-1.731523482346667</v>
       </c>
       <c r="Q73">
-        <v>-1.537134609906667</v>
+        <v>-1.574523482346667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3241714336182282</v>
+        <v>0.3341132705331649</v>
       </c>
       <c r="T73">
-        <v>6.428901469243146</v>
+        <v>6.658505093144687</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07453370660744889</v>
+        <v>0.07349851623790099</v>
       </c>
       <c r="W73">
-        <v>0.2182249519819636</v>
+        <v>0.218469049871103</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3618141097448975</v>
+        <v>0.3567889137762184</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7435,22 +7435,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2508494316564803</v>
+        <v>0.2527494316564803</v>
       </c>
       <c r="C74">
-        <v>-6.226918205689882</v>
+        <v>-6.500263324148037</v>
       </c>
       <c r="D74">
-        <v>8.021481794310116</v>
+        <v>7.947836675851963</v>
       </c>
       <c r="E74">
-        <v>11.7084</v>
+        <v>11.9081</v>
       </c>
       <c r="F74">
-        <v>14.3784</v>
+        <v>14.5781</v>
       </c>
       <c r="G74">
         <v>0.13</v>
@@ -7471,37 +7471,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M74">
-        <v>3.39042672</v>
+        <v>3.43751598</v>
       </c>
       <c r="N74">
-        <v>-2.180760053333333</v>
+        <v>-2.227849313333333</v>
       </c>
       <c r="O74">
-        <v>-0.4492365709866666</v>
+        <v>-0.4589369585466667</v>
       </c>
       <c r="P74">
-        <v>-1.731523482346667</v>
+        <v>-1.768912354786667</v>
       </c>
       <c r="Q74">
-        <v>-1.574523482346667</v>
+        <v>-1.611912354786667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3341132705331649</v>
+        <v>0.344791539812171</v>
       </c>
       <c r="T74">
-        <v>6.658505093144687</v>
+        <v>6.905116392890787</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07349851623790099</v>
+        <v>0.07249168724834069</v>
       </c>
       <c r="W74">
-        <v>0.218469049871103</v>
+        <v>0.2187064601468413</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3567889137762184</v>
+        <v>0.3519013944094208</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7517,22 +7517,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2527494316564803</v>
+        <v>0.2546494316564802</v>
       </c>
       <c r="C75">
-        <v>-6.500263324148037</v>
+        <v>-6.772268475109406</v>
       </c>
       <c r="D75">
-        <v>7.947836675851963</v>
+        <v>7.875531524890593</v>
       </c>
       <c r="E75">
-        <v>11.9081</v>
+        <v>12.1078</v>
       </c>
       <c r="F75">
-        <v>14.5781</v>
+        <v>14.7778</v>
       </c>
       <c r="G75">
         <v>0.13</v>
@@ -7553,37 +7553,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M75">
-        <v>3.43751598</v>
+        <v>3.48460524</v>
       </c>
       <c r="N75">
-        <v>-2.227849313333333</v>
+        <v>-2.274938573333333</v>
       </c>
       <c r="O75">
-        <v>-0.4589369585466667</v>
+        <v>-0.4686373461066667</v>
       </c>
       <c r="P75">
-        <v>-1.768912354786667</v>
+        <v>-1.806301227226667</v>
       </c>
       <c r="Q75">
-        <v>-1.611912354786667</v>
+        <v>-1.649301227226667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.344791539812171</v>
+        <v>0.3562912144203314</v>
       </c>
       <c r="T75">
-        <v>6.905116392890787</v>
+        <v>7.170697792617355</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07249168724834069</v>
+        <v>0.07151206985309284</v>
       </c>
       <c r="W75">
-        <v>0.2187064601468413</v>
+        <v>0.2189374539286407</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3519013944094208</v>
+        <v>0.3471459701606449</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7599,22 +7599,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2546494316564802</v>
+        <v>0.2565494316564803</v>
       </c>
       <c r="C76">
-        <v>-6.772268475109406</v>
+        <v>-7.042969899785526</v>
       </c>
       <c r="D76">
-        <v>7.875531524890593</v>
+        <v>7.804530100214473</v>
       </c>
       <c r="E76">
-        <v>12.1078</v>
+        <v>12.3075</v>
       </c>
       <c r="F76">
-        <v>14.7778</v>
+        <v>14.9775</v>
       </c>
       <c r="G76">
         <v>0.13</v>
@@ -7635,37 +7635,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M76">
-        <v>3.48460524</v>
+        <v>3.5316945</v>
       </c>
       <c r="N76">
-        <v>-2.274938573333333</v>
+        <v>-2.322027833333333</v>
       </c>
       <c r="O76">
-        <v>-0.4686373461066667</v>
+        <v>-0.4783377336666667</v>
       </c>
       <c r="P76">
-        <v>-1.806301227226667</v>
+        <v>-1.843690099666667</v>
       </c>
       <c r="Q76">
-        <v>-1.649301227226667</v>
+        <v>-1.686690099666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3562912144203314</v>
+        <v>0.3687108629971447</v>
       </c>
       <c r="T76">
-        <v>7.170697792617355</v>
+        <v>7.45752570432205</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07151206985309284</v>
+        <v>0.07055857558838494</v>
       </c>
       <c r="W76">
-        <v>0.2189374539286407</v>
+        <v>0.2191622878762588</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3471459701606449</v>
+        <v>0.3425173572251696</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7681,22 +7681,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2565494316564803</v>
+        <v>0.2584494316564803</v>
       </c>
       <c r="C77">
-        <v>-7.042969899785526</v>
+        <v>-7.312402544142468</v>
       </c>
       <c r="D77">
-        <v>7.804530100214473</v>
+        <v>7.734797455857532</v>
       </c>
       <c r="E77">
-        <v>12.3075</v>
+        <v>12.5072</v>
       </c>
       <c r="F77">
-        <v>14.9775</v>
+        <v>15.1772</v>
       </c>
       <c r="G77">
         <v>0.13</v>
@@ -7717,37 +7717,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M77">
-        <v>3.5316945</v>
+        <v>3.57878376</v>
       </c>
       <c r="N77">
-        <v>-2.322027833333333</v>
+        <v>-2.369117093333333</v>
       </c>
       <c r="O77">
-        <v>-0.4783377336666667</v>
+        <v>-0.4880381212266667</v>
       </c>
       <c r="P77">
-        <v>-1.843690099666667</v>
+        <v>-1.881078972106667</v>
       </c>
       <c r="Q77">
-        <v>-1.686690099666666</v>
+        <v>-1.724078972106667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3687108629971447</v>
+        <v>0.3821654822886924</v>
       </c>
       <c r="T77">
-        <v>7.45752570432205</v>
+        <v>7.768255942002136</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07055857558838494</v>
+        <v>0.06963017327801145</v>
       </c>
       <c r="W77">
-        <v>0.2191622878762588</v>
+        <v>0.2193812051410449</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3425173572251696</v>
+        <v>0.3380105498932595</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7763,22 +7763,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2584494316564803</v>
+        <v>0.2603494316564803</v>
       </c>
       <c r="C78">
-        <v>-7.312402544142468</v>
+        <v>-7.580600116252842</v>
       </c>
       <c r="D78">
-        <v>7.734797455857532</v>
+        <v>7.666299883747158</v>
       </c>
       <c r="E78">
-        <v>12.5072</v>
+        <v>12.7069</v>
       </c>
       <c r="F78">
-        <v>15.1772</v>
+        <v>15.3769</v>
       </c>
       <c r="G78">
         <v>0.13</v>
@@ -7799,37 +7799,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M78">
-        <v>3.57878376</v>
+        <v>3.62587302</v>
       </c>
       <c r="N78">
-        <v>-2.369117093333333</v>
+        <v>-2.416206353333333</v>
       </c>
       <c r="O78">
-        <v>-0.4880381212266667</v>
+        <v>-0.4977385087866666</v>
       </c>
       <c r="P78">
-        <v>-1.881078972106667</v>
+        <v>-1.918467844546667</v>
       </c>
       <c r="Q78">
-        <v>-1.724078972106667</v>
+        <v>-1.761467844546666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3821654822886924</v>
+        <v>0.3967900684751574</v>
       </c>
       <c r="T78">
-        <v>7.768255942002136</v>
+        <v>8.106006200350055</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06963017327801145</v>
+        <v>0.06872588531336195</v>
       </c>
       <c r="W78">
-        <v>0.2193812051410449</v>
+        <v>0.2195944362431093</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3380105498932595</v>
+        <v>0.3336208024920483</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7845,22 +7845,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2603494316564803</v>
+        <v>0.2622494316564803</v>
       </c>
       <c r="C79">
-        <v>-7.580600116252842</v>
+        <v>-7.847595140627111</v>
       </c>
       <c r="D79">
-        <v>7.666299883747158</v>
+        <v>7.599004859372888</v>
       </c>
       <c r="E79">
-        <v>12.7069</v>
+        <v>12.9066</v>
       </c>
       <c r="F79">
-        <v>15.3769</v>
+        <v>15.5766</v>
       </c>
       <c r="G79">
         <v>0.13</v>
@@ -7881,37 +7881,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M79">
-        <v>3.62587302</v>
+        <v>3.67296228</v>
       </c>
       <c r="N79">
-        <v>-2.416206353333333</v>
+        <v>-2.463295613333333</v>
       </c>
       <c r="O79">
-        <v>-0.4977385087866666</v>
+        <v>-0.5074388963466667</v>
       </c>
       <c r="P79">
-        <v>-1.918467844546667</v>
+        <v>-1.955856716986667</v>
       </c>
       <c r="Q79">
-        <v>-1.761467844546666</v>
+        <v>-1.798856716986667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3967900684751574</v>
+        <v>0.4127441624967553</v>
       </c>
       <c r="T79">
-        <v>8.106006200350055</v>
+        <v>8.474461027638693</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06872588531336195</v>
+        <v>0.0678447842196009</v>
       </c>
       <c r="W79">
-        <v>0.2195944362431093</v>
+        <v>0.2198021998810181</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3336208024920483</v>
+        <v>0.3293436127165092</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7927,22 +7927,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2622494316564803</v>
+        <v>0.2641494316564803</v>
       </c>
       <c r="C80">
-        <v>-7.847595140627111</v>
+        <v>-8.113419009708316</v>
       </c>
       <c r="D80">
-        <v>7.599004859372888</v>
+        <v>7.532880990291684</v>
       </c>
       <c r="E80">
-        <v>12.9066</v>
+        <v>13.1063</v>
       </c>
       <c r="F80">
-        <v>15.5766</v>
+        <v>15.7763</v>
       </c>
       <c r="G80">
         <v>0.13</v>
@@ -7963,37 +7963,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M80">
-        <v>3.67296228</v>
+        <v>3.72005154</v>
       </c>
       <c r="N80">
-        <v>-2.463295613333333</v>
+        <v>-2.510384873333333</v>
       </c>
       <c r="O80">
-        <v>-0.5074388963466667</v>
+        <v>-0.5171392839066667</v>
       </c>
       <c r="P80">
-        <v>-1.955856716986667</v>
+        <v>-1.993245589426667</v>
       </c>
       <c r="Q80">
-        <v>-1.798856716986667</v>
+        <v>-1.836245589426666</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4127441624967553</v>
+        <v>0.4302176940442199</v>
       </c>
       <c r="T80">
-        <v>8.474461027638693</v>
+        <v>8.878006790859585</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0678447842196009</v>
+        <v>0.06698598948264392</v>
       </c>
       <c r="W80">
-        <v>0.2198021998810181</v>
+        <v>0.2200047036799926</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3293436127165092</v>
+        <v>0.3251747062264269</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8009,22 +8009,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2641494316564803</v>
+        <v>0.2660494316564803</v>
       </c>
       <c r="C81">
-        <v>-8.113419009708316</v>
+        <v>-8.378102032701435</v>
       </c>
       <c r="D81">
-        <v>7.532880990291684</v>
+        <v>7.467897967298565</v>
       </c>
       <c r="E81">
-        <v>13.1063</v>
+        <v>13.306</v>
       </c>
       <c r="F81">
-        <v>15.7763</v>
+        <v>15.976</v>
       </c>
       <c r="G81">
         <v>0.13</v>
@@ -8045,37 +8045,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M81">
-        <v>3.72005154</v>
+        <v>3.7671408</v>
       </c>
       <c r="N81">
-        <v>-2.510384873333333</v>
+        <v>-2.557474133333333</v>
       </c>
       <c r="O81">
-        <v>-0.5171392839066667</v>
+        <v>-0.5268396714666667</v>
       </c>
       <c r="P81">
-        <v>-1.993245589426667</v>
+        <v>-2.030634461866667</v>
       </c>
       <c r="Q81">
-        <v>-1.836245589426666</v>
+        <v>-1.873634461866667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4302176940442199</v>
+        <v>0.4494385787464311</v>
       </c>
       <c r="T81">
-        <v>8.878006790859585</v>
+        <v>9.321907130402566</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06698598948264392</v>
+        <v>0.06614866461411088</v>
       </c>
       <c r="W81">
-        <v>0.2200047036799926</v>
+        <v>0.2202021448839927</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3251747062264269</v>
+        <v>0.3211100223985965</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8091,22 +8091,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2660494316564803</v>
+        <v>0.2679494316564803</v>
       </c>
       <c r="C82">
-        <v>-8.378102032701435</v>
+        <v>-8.641673481896984</v>
       </c>
       <c r="D82">
-        <v>7.467897967298565</v>
+        <v>7.404026518103015</v>
       </c>
       <c r="E82">
-        <v>13.306</v>
+        <v>13.5057</v>
       </c>
       <c r="F82">
-        <v>15.976</v>
+        <v>16.1757</v>
       </c>
       <c r="G82">
         <v>0.13</v>
@@ -8127,37 +8127,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M82">
-        <v>3.7671408</v>
+        <v>3.81423006</v>
       </c>
       <c r="N82">
-        <v>-2.557474133333333</v>
+        <v>-2.604563393333333</v>
       </c>
       <c r="O82">
-        <v>-0.5268396714666667</v>
+        <v>-0.5365400590266667</v>
       </c>
       <c r="P82">
-        <v>-2.030634461866667</v>
+        <v>-2.068023334306667</v>
       </c>
       <c r="Q82">
-        <v>-1.873634461866667</v>
+        <v>-1.911023334306666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4494385787464311</v>
+        <v>0.4706827144699274</v>
       </c>
       <c r="T82">
-        <v>9.321907130402566</v>
+        <v>9.812533821476386</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06614866461411088</v>
+        <v>0.06533201443368977</v>
       </c>
       <c r="W82">
-        <v>0.2202021448839927</v>
+        <v>0.220394710996536</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3211100223985965</v>
+        <v>0.3171457011344163</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8173,22 +8173,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2679494316564803</v>
+        <v>0.2698494316564803</v>
       </c>
       <c r="C83">
-        <v>-8.641673481896984</v>
+        <v>-8.904161636637607</v>
       </c>
       <c r="D83">
-        <v>7.404026518103015</v>
+        <v>7.341238363362391</v>
       </c>
       <c r="E83">
-        <v>13.5057</v>
+        <v>13.7054</v>
       </c>
       <c r="F83">
-        <v>16.1757</v>
+        <v>16.3754</v>
       </c>
       <c r="G83">
         <v>0.13</v>
@@ -8209,37 +8209,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M83">
-        <v>3.81423006</v>
+        <v>3.86131932</v>
       </c>
       <c r="N83">
-        <v>-2.604563393333333</v>
+        <v>-2.651652653333333</v>
       </c>
       <c r="O83">
-        <v>-0.5365400590266667</v>
+        <v>-0.5462404465866667</v>
       </c>
       <c r="P83">
-        <v>-2.068023334306667</v>
+        <v>-2.105412206746666</v>
       </c>
       <c r="Q83">
-        <v>-1.911023334306666</v>
+        <v>-1.948412206746666</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4706827144699274</v>
+        <v>0.4942873097182566</v>
       </c>
       <c r="T83">
-        <v>9.812533821476386</v>
+        <v>10.35767458933618</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06533201443368977</v>
+        <v>0.06453528255035208</v>
       </c>
       <c r="W83">
-        <v>0.220394710996536</v>
+        <v>0.220582580374627</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3171457011344163</v>
+        <v>0.3132780706327771</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8255,22 +8255,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2698494316564803</v>
+        <v>0.2717494316564803</v>
       </c>
       <c r="C84">
-        <v>-8.904161636637607</v>
+        <v>-9.165593825066365</v>
       </c>
       <c r="D84">
-        <v>7.341238363362391</v>
+        <v>7.279506174933634</v>
       </c>
       <c r="E84">
-        <v>13.7054</v>
+        <v>13.9051</v>
       </c>
       <c r="F84">
-        <v>16.3754</v>
+        <v>16.5751</v>
       </c>
       <c r="G84">
         <v>0.13</v>
@@ -8291,37 +8291,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M84">
-        <v>3.86131932</v>
+        <v>3.90840858</v>
       </c>
       <c r="N84">
-        <v>-2.651652653333333</v>
+        <v>-2.698741913333333</v>
       </c>
       <c r="O84">
-        <v>-0.5462404465866667</v>
+        <v>-0.5559408341466667</v>
       </c>
       <c r="P84">
-        <v>-2.105412206746666</v>
+        <v>-2.142801079186667</v>
       </c>
       <c r="Q84">
-        <v>-1.948412206746666</v>
+        <v>-1.985801079186666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4942873097182566</v>
+        <v>0.5206689161722717</v>
       </c>
       <c r="T84">
-        <v>10.35767458933618</v>
+        <v>10.96694956517949</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06453528255035208</v>
+        <v>0.06375774902564904</v>
       </c>
       <c r="W84">
-        <v>0.220582580374627</v>
+        <v>0.220765922779752</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3132780706327771</v>
+        <v>0.3095036360468399</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8337,22 +8337,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2717494316564803</v>
+        <v>0.2736494316564803</v>
       </c>
       <c r="C85">
-        <v>-9.165593825066365</v>
+        <v>-9.425996463786248</v>
       </c>
       <c r="D85">
-        <v>7.279506174933634</v>
+        <v>7.218803536213751</v>
       </c>
       <c r="E85">
-        <v>13.9051</v>
+        <v>14.1048</v>
       </c>
       <c r="F85">
-        <v>16.5751</v>
+        <v>16.7748</v>
       </c>
       <c r="G85">
         <v>0.13</v>
@@ -8373,37 +8373,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M85">
-        <v>3.90840858</v>
+        <v>3.95549784</v>
       </c>
       <c r="N85">
-        <v>-2.698741913333333</v>
+        <v>-2.745831173333333</v>
       </c>
       <c r="O85">
-        <v>-0.5559408341466667</v>
+        <v>-0.5656412217066668</v>
       </c>
       <c r="P85">
-        <v>-2.142801079186667</v>
+        <v>-2.180189951626667</v>
       </c>
       <c r="Q85">
-        <v>-1.985801079186666</v>
+        <v>-2.023189951626667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5206689161722717</v>
+        <v>0.5503482234330388</v>
       </c>
       <c r="T85">
-        <v>10.96694956517949</v>
+        <v>11.65238391300321</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06375774902564904</v>
+        <v>0.06299872820391512</v>
       </c>
       <c r="W85">
-        <v>0.220765922779752</v>
+        <v>0.2209448998895168</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3095036360468399</v>
+        <v>0.3058190689510443</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8419,22 +8419,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2736494316564803</v>
+        <v>0.2755494316564803</v>
       </c>
       <c r="C86">
-        <v>-9.425996463786245</v>
+        <v>-9.685395095551804</v>
       </c>
       <c r="D86">
-        <v>7.218803536213754</v>
+        <v>7.159104904448195</v>
       </c>
       <c r="E86">
-        <v>14.1048</v>
+        <v>14.3045</v>
       </c>
       <c r="F86">
-        <v>16.7748</v>
+        <v>16.9745</v>
       </c>
       <c r="G86">
         <v>0.13</v>
@@ -8455,37 +8455,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M86">
-        <v>3.95549784</v>
+        <v>4.0025871</v>
       </c>
       <c r="N86">
-        <v>-2.745831173333333</v>
+        <v>-2.792920433333333</v>
       </c>
       <c r="O86">
-        <v>-0.5656412217066668</v>
+        <v>-0.5753416092666667</v>
       </c>
       <c r="P86">
-        <v>-2.180189951626667</v>
+        <v>-2.217578824066666</v>
       </c>
       <c r="Q86">
-        <v>-2.023189951626667</v>
+        <v>-2.060578824066666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5503482234330385</v>
+        <v>0.5839847716619078</v>
       </c>
       <c r="T86">
-        <v>11.6523839130032</v>
+        <v>12.42920950720342</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06299872820391512</v>
+        <v>0.06225756669563377</v>
       </c>
       <c r="W86">
-        <v>0.2209448998895168</v>
+        <v>0.2211196657731696</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3058190689510443</v>
+        <v>0.3022211975516202</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8501,22 +8501,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2755494316564803</v>
+        <v>0.2774494316564803</v>
       </c>
       <c r="C87">
-        <v>-9.685395095551804</v>
+        <v>-9.943814425105881</v>
       </c>
       <c r="D87">
-        <v>7.159104904448195</v>
+        <v>7.100385574894118</v>
       </c>
       <c r="E87">
-        <v>14.3045</v>
+        <v>14.5042</v>
       </c>
       <c r="F87">
-        <v>16.9745</v>
+        <v>17.1742</v>
       </c>
       <c r="G87">
         <v>0.13</v>
@@ -8537,37 +8537,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M87">
-        <v>4.0025871</v>
+        <v>4.04967636</v>
       </c>
       <c r="N87">
-        <v>-2.792920433333333</v>
+        <v>-2.840009693333334</v>
       </c>
       <c r="O87">
-        <v>-0.5753416092666667</v>
+        <v>-0.5850419968266668</v>
       </c>
       <c r="P87">
-        <v>-2.217578824066666</v>
+        <v>-2.254967696506667</v>
       </c>
       <c r="Q87">
-        <v>-2.060578824066666</v>
+        <v>-2.097967696506667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5839847716619078</v>
+        <v>0.6224265410663298</v>
       </c>
       <c r="T87">
-        <v>12.42920950720342</v>
+        <v>13.31701018628937</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06225756669563377</v>
+        <v>0.06153364150149849</v>
       </c>
       <c r="W87">
-        <v>0.2211196657731696</v>
+        <v>0.2212903673339467</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3022211975516202</v>
+        <v>0.2987069975800897</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8583,22 +8583,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2774494316564803</v>
+        <v>0.2793494316564803</v>
       </c>
       <c r="C88">
-        <v>-9.943814425105881</v>
+        <v>-10.2012783532671</v>
       </c>
       <c r="D88">
-        <v>7.100385574894118</v>
+        <v>7.042621646732898</v>
       </c>
       <c r="E88">
-        <v>14.5042</v>
+        <v>14.7039</v>
       </c>
       <c r="F88">
-        <v>17.1742</v>
+        <v>17.3739</v>
       </c>
       <c r="G88">
         <v>0.13</v>
@@ -8619,37 +8619,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M88">
-        <v>4.04967636</v>
+        <v>4.09676562</v>
       </c>
       <c r="N88">
-        <v>-2.840009693333334</v>
+        <v>-2.887098953333334</v>
       </c>
       <c r="O88">
-        <v>-0.5850419968266668</v>
+        <v>-0.5947423843866667</v>
       </c>
       <c r="P88">
-        <v>-2.254967696506667</v>
+        <v>-2.292356568946667</v>
       </c>
       <c r="Q88">
-        <v>-2.097967696506667</v>
+        <v>-2.135356568946667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6224265410663298</v>
+        <v>0.6667824288406629</v>
       </c>
       <c r="T88">
-        <v>13.31701018628937</v>
+        <v>14.34139558523471</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06153364150149849</v>
+        <v>0.06082635826584908</v>
       </c>
       <c r="W88">
-        <v>0.2212903673339467</v>
+        <v>0.2214571447209128</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2987069975800897</v>
+        <v>0.2952735838148014</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8665,22 +8665,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2793494316564803</v>
+        <v>0.2812494316564803</v>
       </c>
       <c r="C89">
-        <v>-10.2012783532671</v>
+        <v>-10.45781000936689</v>
       </c>
       <c r="D89">
-        <v>7.042621646732898</v>
+        <v>6.985789990633106</v>
       </c>
       <c r="E89">
-        <v>14.7039</v>
+        <v>14.9036</v>
       </c>
       <c r="F89">
-        <v>17.3739</v>
+        <v>17.5736</v>
       </c>
       <c r="G89">
         <v>0.13</v>
@@ -8701,37 +8701,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M89">
-        <v>4.09676562</v>
+        <v>4.14385488</v>
       </c>
       <c r="N89">
-        <v>-2.887098953333334</v>
+        <v>-2.934188213333333</v>
       </c>
       <c r="O89">
-        <v>-0.5947423843866667</v>
+        <v>-0.6044427719466667</v>
       </c>
       <c r="P89">
-        <v>-2.292356568946667</v>
+        <v>-2.329745441386667</v>
       </c>
       <c r="Q89">
-        <v>-2.135356568946667</v>
+        <v>-2.172745441386667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6667824288406629</v>
+        <v>0.7185309645773847</v>
       </c>
       <c r="T89">
-        <v>14.34139558523471</v>
+        <v>15.53651188400427</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06082635826584908</v>
+        <v>0.06013514964919171</v>
       </c>
       <c r="W89">
-        <v>0.2214571447209128</v>
+        <v>0.2216201317127206</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2952735838148014</v>
+        <v>0.2919182021805422</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8747,22 +8747,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2812494316564803</v>
+        <v>0.2831494316564803</v>
       </c>
       <c r="C90">
-        <v>-10.45781000936689</v>
+        <v>-10.71343178212855</v>
       </c>
       <c r="D90">
-        <v>6.985789990633106</v>
+        <v>6.929868217871445</v>
       </c>
       <c r="E90">
-        <v>14.9036</v>
+        <v>15.1033</v>
       </c>
       <c r="F90">
-        <v>17.5736</v>
+        <v>17.7733</v>
       </c>
       <c r="G90">
         <v>0.13</v>
@@ -8783,37 +8783,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M90">
-        <v>4.14385488</v>
+        <v>4.19094414</v>
       </c>
       <c r="N90">
-        <v>-2.934188213333333</v>
+        <v>-2.981277473333333</v>
       </c>
       <c r="O90">
-        <v>-0.6044427719466667</v>
+        <v>-0.6141431595066668</v>
       </c>
       <c r="P90">
-        <v>-2.329745441386667</v>
+        <v>-2.367134313826667</v>
       </c>
       <c r="Q90">
-        <v>-2.172745441386667</v>
+        <v>-2.210134313826666</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7185309645773847</v>
+        <v>0.7796883249935106</v>
       </c>
       <c r="T90">
-        <v>15.53651188400427</v>
+        <v>16.94892205527739</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06013514964919171</v>
+        <v>0.05945947381043674</v>
       </c>
       <c r="W90">
-        <v>0.2216201317127206</v>
+        <v>0.221779456075499</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2919182021805422</v>
+        <v>0.2886382223807609</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8829,22 +8829,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2831494316564803</v>
+        <v>0.2850494316564803</v>
       </c>
       <c r="C91">
-        <v>-10.71343178212855</v>
+        <v>-10.96816534907496</v>
       </c>
       <c r="D91">
-        <v>6.929868217871445</v>
+        <v>6.874834650925042</v>
       </c>
       <c r="E91">
-        <v>15.1033</v>
+        <v>15.303</v>
       </c>
       <c r="F91">
-        <v>17.7733</v>
+        <v>17.973</v>
       </c>
       <c r="G91">
         <v>0.13</v>
@@ -8865,37 +8865,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M91">
-        <v>4.19094414</v>
+        <v>4.2380334</v>
       </c>
       <c r="N91">
-        <v>-2.981277473333333</v>
+        <v>-3.028366733333333</v>
       </c>
       <c r="O91">
-        <v>-0.6141431595066668</v>
+        <v>-0.6238435470666667</v>
       </c>
       <c r="P91">
-        <v>-2.367134313826667</v>
+        <v>-2.404523186266667</v>
       </c>
       <c r="Q91">
-        <v>-2.210134313826666</v>
+        <v>-2.247523186266667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7796883249935106</v>
+        <v>0.8530771574928618</v>
       </c>
       <c r="T91">
-        <v>16.94892205527739</v>
+        <v>18.64381426080513</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05945947381043674</v>
+        <v>0.05879881299032079</v>
       </c>
       <c r="W91">
-        <v>0.221779456075499</v>
+        <v>0.2219352398968824</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2886382223807609</v>
+        <v>0.2854311310209746</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8911,22 +8911,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2850494316564803</v>
+        <v>0.2869494316564803</v>
       </c>
       <c r="C92">
-        <v>-10.96816534907496</v>
+        <v>-11.22203170454605</v>
       </c>
       <c r="D92">
-        <v>6.874834650925042</v>
+        <v>6.820668295453947</v>
       </c>
       <c r="E92">
-        <v>15.303</v>
+        <v>15.5027</v>
       </c>
       <c r="F92">
-        <v>17.973</v>
+        <v>18.1727</v>
       </c>
       <c r="G92">
         <v>0.13</v>
@@ -8947,37 +8947,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M92">
-        <v>4.2380334</v>
+        <v>4.28512266</v>
       </c>
       <c r="N92">
-        <v>-3.028366733333333</v>
+        <v>-3.075455993333333</v>
       </c>
       <c r="O92">
-        <v>-0.6238435470666667</v>
+        <v>-0.6335439346266667</v>
       </c>
       <c r="P92">
-        <v>-2.404523186266667</v>
+        <v>-2.441912058706666</v>
       </c>
       <c r="Q92">
-        <v>-2.247523186266667</v>
+        <v>-2.284912058706666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8530771574928618</v>
+        <v>0.9427746194365132</v>
       </c>
       <c r="T92">
-        <v>18.64381426080513</v>
+        <v>20.71534917867237</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05879881299032079</v>
+        <v>0.05815267218822935</v>
       </c>
       <c r="W92">
-        <v>0.2219352398968824</v>
+        <v>0.2220875998980155</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2854311310209746</v>
+        <v>0.2822945251855793</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8993,22 +8993,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2869494316564803</v>
+        <v>0.2888494316564803</v>
       </c>
       <c r="C93">
-        <v>-11.22203170454605</v>
+        <v>-11.47505118640223</v>
       </c>
       <c r="D93">
-        <v>6.820668295453947</v>
+        <v>6.767348813597767</v>
       </c>
       <c r="E93">
-        <v>15.5027</v>
+        <v>15.7024</v>
       </c>
       <c r="F93">
-        <v>18.1727</v>
+        <v>18.3724</v>
       </c>
       <c r="G93">
         <v>0.13</v>
@@ -9029,37 +9029,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M93">
-        <v>4.28512266</v>
+        <v>4.33221192</v>
       </c>
       <c r="N93">
-        <v>-3.075455993333333</v>
+        <v>-3.122545253333333</v>
       </c>
       <c r="O93">
-        <v>-0.6335439346266667</v>
+        <v>-0.6432443221866667</v>
       </c>
       <c r="P93">
-        <v>-2.441912058706666</v>
+        <v>-2.479300931146666</v>
       </c>
       <c r="Q93">
-        <v>-2.284912058706666</v>
+        <v>-2.322300931146666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9427746194365132</v>
+        <v>1.054896446866078</v>
       </c>
       <c r="T93">
-        <v>20.71534917867237</v>
+        <v>23.30476782600642</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05815267218822935</v>
+        <v>0.05752057792531381</v>
       </c>
       <c r="W93">
-        <v>0.2220875998980155</v>
+        <v>0.222236647725211</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2822945251855793</v>
+        <v>0.2792261064335622</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9075,22 +9075,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2888494316564803</v>
+        <v>0.2907494316564803</v>
       </c>
       <c r="C94">
-        <v>-11.47505118640223</v>
+        <v>-11.72724350148491</v>
       </c>
       <c r="D94">
-        <v>6.767348813597767</v>
+        <v>6.714856498515085</v>
       </c>
       <c r="E94">
-        <v>15.7024</v>
+        <v>15.9021</v>
       </c>
       <c r="F94">
-        <v>18.3724</v>
+        <v>18.5721</v>
       </c>
       <c r="G94">
         <v>0.13</v>
@@ -9111,37 +9111,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M94">
-        <v>4.33221192</v>
+        <v>4.37930118</v>
       </c>
       <c r="N94">
-        <v>-3.122545253333333</v>
+        <v>-3.169634513333333</v>
       </c>
       <c r="O94">
-        <v>-0.6432443221866667</v>
+        <v>-0.6529447097466666</v>
       </c>
       <c r="P94">
-        <v>-2.479300931146666</v>
+        <v>-2.516689803586666</v>
       </c>
       <c r="Q94">
-        <v>-2.322300931146666</v>
+        <v>-2.359689803586666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.054896446866078</v>
+        <v>1.19905308213266</v>
       </c>
       <c r="T94">
-        <v>23.30476782600642</v>
+        <v>26.63402037257877</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05752057792531381</v>
+        <v>0.05690207708740722</v>
       </c>
       <c r="W94">
-        <v>0.222236647725211</v>
+        <v>0.2223824902227894</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2792261064335622</v>
+        <v>0.2762236751815884</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9157,22 +9157,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2907494316564803</v>
+        <v>0.2926494316564803</v>
       </c>
       <c r="C95">
-        <v>-11.72724350148491</v>
+        <v>-11.97862774990131</v>
       </c>
       <c r="D95">
-        <v>6.714856498515085</v>
+        <v>6.663172250098693</v>
       </c>
       <c r="E95">
-        <v>15.9021</v>
+        <v>16.1018</v>
       </c>
       <c r="F95">
-        <v>18.5721</v>
+        <v>18.7718</v>
       </c>
       <c r="G95">
         <v>0.13</v>
@@ -9193,37 +9193,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M95">
-        <v>4.37930118</v>
+        <v>4.42639044</v>
       </c>
       <c r="N95">
-        <v>-3.169634513333333</v>
+        <v>-3.216723773333333</v>
       </c>
       <c r="O95">
-        <v>-0.6529447097466666</v>
+        <v>-0.6626450973066667</v>
       </c>
       <c r="P95">
-        <v>-2.516689803586666</v>
+        <v>-2.554078676026666</v>
       </c>
       <c r="Q95">
-        <v>-2.359689803586666</v>
+        <v>-2.397078676026666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.19905308213266</v>
+        <v>1.391261929154771</v>
       </c>
       <c r="T95">
-        <v>26.63402037257877</v>
+        <v>31.07302376800857</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05690207708740722</v>
+        <v>0.0562967358417965</v>
       </c>
       <c r="W95">
-        <v>0.2223824902227894</v>
+        <v>0.2225252296885044</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2762236751815884</v>
+        <v>0.273285125445614</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9239,22 +9239,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2926494316564803</v>
+        <v>0.2945494316564803</v>
       </c>
       <c r="C96">
-        <v>-11.97862774990131</v>
+        <v>-12.22922244819622</v>
       </c>
       <c r="D96">
-        <v>6.663172250098693</v>
+        <v>6.612277551803781</v>
       </c>
       <c r="E96">
-        <v>16.1018</v>
+        <v>16.3015</v>
       </c>
       <c r="F96">
-        <v>18.7718</v>
+        <v>18.9715</v>
       </c>
       <c r="G96">
         <v>0.13</v>
@@ -9275,37 +9275,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M96">
-        <v>4.42639044</v>
+        <v>4.4734797</v>
       </c>
       <c r="N96">
-        <v>-3.216723773333333</v>
+        <v>-3.263813033333333</v>
       </c>
       <c r="O96">
-        <v>-0.6626450973066667</v>
+        <v>-0.6723454848666666</v>
       </c>
       <c r="P96">
-        <v>-2.554078676026666</v>
+        <v>-2.591467548466666</v>
       </c>
       <c r="Q96">
-        <v>-2.397078676026666</v>
+        <v>-2.434467548466666</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.391261929154771</v>
+        <v>1.660354314985726</v>
       </c>
       <c r="T96">
-        <v>31.07302376800857</v>
+        <v>37.2876285216103</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0562967358417965</v>
+        <v>0.05570413862240917</v>
       </c>
       <c r="W96">
-        <v>0.2225252296885044</v>
+        <v>0.2226649641128359</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.273285125445614</v>
+        <v>0.2704084399146076</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9321,22 +9321,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2945494316564803</v>
+        <v>0.2964494316564803</v>
       </c>
       <c r="C97">
-        <v>-12.22922244819622</v>
+        <v>-12.47904555146998</v>
       </c>
       <c r="D97">
-        <v>6.612277551803781</v>
+        <v>6.562154448530022</v>
       </c>
       <c r="E97">
-        <v>16.3015</v>
+        <v>16.5012</v>
       </c>
       <c r="F97">
-        <v>18.9715</v>
+        <v>19.1712</v>
       </c>
       <c r="G97">
         <v>0.13</v>
@@ -9357,37 +9357,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M97">
-        <v>4.4734797</v>
+        <v>4.52056896</v>
       </c>
       <c r="N97">
-        <v>-3.263813033333333</v>
+        <v>-3.310902293333334</v>
       </c>
       <c r="O97">
-        <v>-0.6723454848666666</v>
+        <v>-0.6820458724266668</v>
       </c>
       <c r="P97">
-        <v>-2.591467548466666</v>
+        <v>-2.628856420906667</v>
       </c>
       <c r="Q97">
-        <v>-2.434467548466666</v>
+        <v>-2.471856420906667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.660354314985726</v>
+        <v>2.063992893732158</v>
       </c>
       <c r="T97">
-        <v>37.2876285216103</v>
+        <v>46.6095356520129</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05570413862240917</v>
+        <v>0.05512388717842573</v>
       </c>
       <c r="W97">
-        <v>0.2226649641128359</v>
+        <v>0.2228017874033272</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2704084399146076</v>
+        <v>0.2675916853321637</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9403,22 +9403,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2964494316564803</v>
+        <v>0.2983494316564803</v>
       </c>
       <c r="C98">
-        <v>-12.47904555146998</v>
+        <v>-12.72811447449795</v>
       </c>
       <c r="D98">
-        <v>6.562154448530022</v>
+        <v>6.512785525502047</v>
       </c>
       <c r="E98">
-        <v>16.5012</v>
+        <v>16.7009</v>
       </c>
       <c r="F98">
-        <v>19.1712</v>
+        <v>19.3709</v>
       </c>
       <c r="G98">
         <v>0.13</v>
@@ -9439,37 +9439,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M98">
-        <v>4.52056896</v>
+        <v>4.56765822</v>
       </c>
       <c r="N98">
-        <v>-3.310902293333334</v>
+        <v>-3.357991553333334</v>
       </c>
       <c r="O98">
-        <v>-0.6820458724266668</v>
+        <v>-0.6917462599866667</v>
       </c>
       <c r="P98">
-        <v>-2.628856420906667</v>
+        <v>-2.666245293346667</v>
       </c>
       <c r="Q98">
-        <v>-2.471856420906667</v>
+        <v>-2.509245293346667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.063992893732153</v>
+        <v>2.736723858309537</v>
       </c>
       <c r="T98">
-        <v>46.60953565201277</v>
+        <v>62.14604753601703</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05512388717842573</v>
+        <v>0.05455559968174093</v>
       </c>
       <c r="W98">
-        <v>0.2228017874033272</v>
+        <v>0.2229357895950455</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2675916853321637</v>
+        <v>0.2648330081637909</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9485,22 +9485,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2983494316564803</v>
+        <v>0.3002494316564803</v>
       </c>
       <c r="C99">
-        <v>-12.72811447449795</v>
+        <v>-12.97644611190385</v>
       </c>
       <c r="D99">
-        <v>6.512785525502047</v>
+        <v>6.464153888096154</v>
       </c>
       <c r="E99">
-        <v>16.7009</v>
+        <v>16.9006</v>
       </c>
       <c r="F99">
-        <v>19.3709</v>
+        <v>19.5706</v>
       </c>
       <c r="G99">
         <v>0.13</v>
@@ -9521,37 +9521,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M99">
-        <v>4.56765822</v>
+        <v>4.61474748</v>
       </c>
       <c r="N99">
-        <v>-3.357991553333334</v>
+        <v>-3.405080813333333</v>
       </c>
       <c r="O99">
-        <v>-0.6917462599866667</v>
+        <v>-0.7014466475466667</v>
       </c>
       <c r="P99">
-        <v>-2.666245293346667</v>
+        <v>-2.703634165786667</v>
       </c>
       <c r="Q99">
-        <v>-2.509245293346667</v>
+        <v>-2.546634165786667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.736723858309537</v>
+        <v>4.082185787464305</v>
       </c>
       <c r="T99">
-        <v>62.14604753601703</v>
+        <v>93.21907130402555</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05455559968174093</v>
+        <v>0.05399890988907011</v>
       </c>
       <c r="W99">
-        <v>0.2229357895950455</v>
+        <v>0.2230670570481573</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2648330081637909</v>
+        <v>0.2621306305294665</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9567,22 +9567,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3002494316564803</v>
+        <v>0.3021494316564803</v>
       </c>
       <c r="C100">
-        <v>-12.97644611190385</v>
+        <v>-13.22405685743591</v>
       </c>
       <c r="D100">
-        <v>6.464153888096154</v>
+        <v>6.416243142564088</v>
       </c>
       <c r="E100">
-        <v>16.9006</v>
+        <v>17.1003</v>
       </c>
       <c r="F100">
-        <v>19.5706</v>
+        <v>19.7703</v>
       </c>
       <c r="G100">
         <v>0.13</v>
@@ -9603,37 +9603,37 @@
         <v>1.209666666666667</v>
       </c>
       <c r="M100">
-        <v>4.61474748</v>
+        <v>4.66183674</v>
       </c>
       <c r="N100">
-        <v>-3.405080813333333</v>
+        <v>-3.452170073333333</v>
       </c>
       <c r="O100">
-        <v>-0.7014466475466667</v>
+        <v>-0.7111470351066668</v>
       </c>
       <c r="P100">
-        <v>-2.703634165786667</v>
+        <v>-2.741023038226666</v>
       </c>
       <c r="Q100">
-        <v>-2.546634165786667</v>
+        <v>-2.584023038226666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.082185787464305</v>
+        <v>8.118571574928611</v>
       </c>
       <c r="T100">
-        <v>93.21907130402555</v>
+        <v>186.4381426080511</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05399890988907011</v>
+        <v>0.05345346635483708</v>
       </c>
       <c r="W100">
-        <v>0.2230670570481573</v>
+        <v>0.2231956726335294</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9641,91 +9641,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2621306305294665</v>
+        <v>0.2594828463827042</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3021494316564803</v>
-      </c>
-      <c r="C101">
-        <v>-13.22405685743591</v>
-      </c>
-      <c r="D101">
-        <v>6.416243142564088</v>
-      </c>
-      <c r="E101">
-        <v>17.1003</v>
-      </c>
-      <c r="F101">
-        <v>19.7703</v>
-      </c>
-      <c r="G101">
-        <v>0.13</v>
-      </c>
-      <c r="H101">
-        <v>17.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.366666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.1569999999999999</v>
-      </c>
-      <c r="L101">
-        <v>1.209666666666667</v>
-      </c>
-      <c r="M101">
-        <v>4.66183674</v>
-      </c>
-      <c r="N101">
-        <v>-3.452170073333333</v>
-      </c>
-      <c r="O101">
-        <v>-0.7111470351066668</v>
-      </c>
-      <c r="P101">
-        <v>-2.741023038226666</v>
-      </c>
-      <c r="Q101">
-        <v>-2.584023038226666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.118571574928611</v>
-      </c>
-      <c r="T101">
-        <v>186.4381426080511</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05345346635483708</v>
-      </c>
-      <c r="W101">
-        <v>0.2231956726335294</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2594828463827042</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
